--- a/docs/fourth-estate-cards.xlsx
+++ b/docs/fourth-estate-cards.xlsx
@@ -10,13 +10,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elections" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newspapers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newspapers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stories'!$A$1:$AC$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Elections'!$A$1:$AD$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Newspapers'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Elections'!$A$1:$L$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Candidates'!$A$1:$U$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Newspapers'!$A$1:$F$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -475,7 +477,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Exported from docs/deck-dc.csv, docs/elections-dc.csv and docs/papers-dc.csv on the variant branch.</t>
+          <t>Exported from docs/deck-dc.csv, docs/elections-dc.csv, docs/candidates-dc.csv and docs/papers-dc.csv on the variant branch.</t>
         </is>
       </c>
     </row>
@@ -513,146 +515,170 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Elections -- the 17 election cards: two candidates each, thresholds, the card's power and its First Appearance event.</t>
+          <t>Elections -- the 17 elections: the two candidates, history's choice, and the First Appearance event when the campaign opens.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Newspapers -- the eight papers (DC's Super Heroes) and their abilities.</t>
+          <t>Candidates -- the 34 candidates, each his own card: theme, threshold, the card's prestige and its power, one column per effect.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Newspapers -- the eight papers (DC's Super Heroes) and their abilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>Summary -- counts by type, theme and era, as formulas over the Stories sheet.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Stories columns</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>cost = price on the exchange; Prestige = the score; Influence (plain) = spends on anything;</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Political / Economic / Social influence = influence of that theme (a story has at most one); Campaign influence = elections only;</t>
+          <t>cost = price on the exchange; Prestige = the score; Influence (plain) = spends on anything;</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>draw = cards drawn; trash = cards you may destroy; gain_upto = gain a story costing that or less;</t>
+          <t>Political / Economic / Social influence = influence of that theme (a story has at most one); Campaign influence = elections only;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>chain = +N if you play another story of the theme; per_same = +N per other story of the theme; per_office = +N per election won;</t>
+          <t>draw = cards drawn; trash = cards you may destroy; gain_upto = gain a story costing that or less;</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>attack = discard or scandal (hits every rival); defense = 1 if it blocks an attack; retract = Retraction (draw a card, destroy a Scandal);</t>
+          <t>chain = +N if you play another story of the theme; per_same = +N per other story of the theme; per_office = +N per election won;</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ongoing_gen / ongoing_draw = a media event's bonus to its owner each turn; others_bonus / others_theme = its bonus to every other paper;</t>
+          <t>attack = discard or scandal (hits every rival); defense = 1 if it blocks an attack; retract = Retraction (draw a card, destroy a Scandal);</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>ongoing_gen / ongoing_draw = a media event's bonus to its owner each turn; others_bonus / others_theme = its bonus to every other paper;</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>released = the election whose campaign releases it into the main deck; year = the event's date; copies = how many exist.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Elections columns</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>nation / states = the two candidates; *_theme = the influence that counts toward him; *_threshold = influence needed to elect him.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>historical_winner = history's choice (2 cheaper); Prestige = the card's prestige; Prestige per office = prestige for each election card held (1860);</t>
+          <t>nation / states = the two candidates (their cards are on the Candidates sheet); historical_winner = history's choice (2 cheaper);</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Influence (plain) = its plain influence when played; Candidate-theme influence = influence of the elected candidate's theme when played.</t>
+          <t>First Appearance = what happens to every paper as the campaign opens; fa_kind = which event: discard, discard_leader, discard_dearest,</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>p_* = the rest of the card's power when played: p_draw, p_trash (destroy up to N), p_trash_draw (draw one per card destroyed),</t>
+          <t>destroy_cheapest, draw, draw_fewest, scandal, scandal_leader, unscandal, sweep; First Appearance: how many = its number.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>p_gain_upto, p_recover (cards from discard to hand), p_per_kind (+N per different kind of card played), p_scry (look at the top N, keep 1),</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>p_stay_gen (stays in play: +N each turn; none now), p_attack.</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Candidates columns</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>fa_kind / fa_n = the First Appearance when the campaign opens: discard, discard_leader, discard_dearest, destroy_cheapest, draw, draw_fewest,</t>
+          <t>key = year-side; theme = the influence that counts toward him; threshold = influence needed to elect him; card_name = his card;</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>scandal, scandal_leader, unscandal, sweep; fa_n = how many.</t>
+          <t>Prestige = the card's prestige; Prestige per office = prestige for each election card its holder owns (1860);</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>the power when played: Influence (plain); Candidate-theme influence (his theme); Draw; Destroy (up to N cards from hand or discard);</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Draw per destroyed (1 = draw a card for each); Gain (cost up to) a story from the exchange; Recover (cards from discard to hand);</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Per kind played (+N per different kind of card played this turn); Look at top (look at the top N of the main deck, keep 1);</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Stays in play (+N each turn; none now); Attack (discard or scandal, every rival); Power = the card's text.</t>
         </is>
       </c>
     </row>
@@ -11598,39 +11624,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD18"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="9" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="50" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="24" customWidth="1" min="28" max="28"/>
-    <col width="45" customWidth="1" min="29" max="29"/>
-    <col width="60" customWidth="1" min="30" max="30"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -11651,137 +11659,47 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>card_name</t>
+          <t>nation</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>Prestige</t>
+          <t>nation card</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>Prestige per office</t>
+          <t>states</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>Influence (plain)</t>
+          <t>states card</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>Candidate-theme influence</t>
+          <t>historical_winner</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>nation</t>
+          <t>fa_name</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>nation_theme</t>
+          <t>First Appearance</t>
         </is>
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
-          <t>nation_threshold</t>
+          <t>fa_kind</t>
         </is>
       </c>
       <c r="L1" s="4" t="inlineStr">
         <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>states_theme</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>states_threshold</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>historical_winner</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>p_draw</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>p_trash</t>
-        </is>
-      </c>
-      <c r="R1" s="4" t="inlineStr">
-        <is>
-          <t>p_trash_draw</t>
-        </is>
-      </c>
-      <c r="S1" s="4" t="inlineStr">
-        <is>
-          <t>p_gain_upto</t>
-        </is>
-      </c>
-      <c r="T1" s="4" t="inlineStr">
-        <is>
-          <t>p_recover</t>
-        </is>
-      </c>
-      <c r="U1" s="4" t="inlineStr">
-        <is>
-          <t>p_per_kind</t>
-        </is>
-      </c>
-      <c r="V1" s="4" t="inlineStr">
-        <is>
-          <t>p_scry</t>
-        </is>
-      </c>
-      <c r="W1" s="4" t="inlineStr">
-        <is>
-          <t>p_stay_gen</t>
-        </is>
-      </c>
-      <c r="X1" s="4" t="inlineStr">
-        <is>
-          <t>p_attack</t>
-        </is>
-      </c>
-      <c r="Y1" s="4" t="inlineStr">
-        <is>
-          <t>power_text</t>
-        </is>
-      </c>
-      <c r="Z1" s="4" t="inlineStr">
-        <is>
-          <t>fa_kind</t>
-        </is>
-      </c>
-      <c r="AA1" s="4" t="inlineStr">
-        <is>
-          <t>fa_n</t>
-        </is>
-      </c>
-      <c r="AB1" s="4" t="inlineStr">
-        <is>
-          <t>fa_name</t>
-        </is>
-      </c>
-      <c r="AC1" s="4" t="inlineStr">
-        <is>
-          <t>fa_text</t>
-        </is>
-      </c>
-      <c r="AD1" s="4" t="inlineStr">
-        <is>
-          <t>card_text</t>
+          <t>First Appearance: how many</t>
         </is>
       </c>
     </row>
@@ -11799,92 +11717,34 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>The Farewell Address</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
           <t>John Adams</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>The Federalist Administration</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Thomas Jefferson</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>The Republican Societies</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>nation</t>
         </is>
       </c>
-      <c r="P2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" s="5" t="n"/>
-      <c r="Y2" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence, draw a card.</t>
-        </is>
-      </c>
-      <c r="Z2" s="5" t="n"/>
-      <c r="AA2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="6" t="n"/>
-      <c r="AC2" s="6" t="n"/>
-      <c r="AD2" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence, draw a card. Also +2 of the elected candidate's theme. Worth 3 prestige.</t>
-        </is>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -11901,104 +11761,46 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
+          <t>John Adams</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>The Alien and Sedition Acts</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
           <t>The Revolution of 1800</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>2</v>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>John Adams</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" s="5" t="n"/>
-      <c r="Y3" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence, draw 2 cards, then you may destroy a card in your hand or discard pile.</t>
-        </is>
-      </c>
-      <c r="Z3" s="5" t="inlineStr">
+          <t>The Sedition Act</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards a card at random.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>discard_leader</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="6" t="inlineStr">
-        <is>
-          <t>The Sedition Act</t>
-        </is>
-      </c>
-      <c r="AC3" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards a card at random.</t>
-        </is>
-      </c>
-      <c r="AD3" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence, draw 2 cards, then you may destroy a card in your hand or discard pile. Also +2 of the elected candidate's theme. Worth 3 prestige.</t>
-        </is>
+      <c r="L3" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -12015,104 +11817,46 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
+          <t>Thomas Jefferson</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
           <t>The Louisiana Purchase</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>2</v>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Charles C. Pinckney</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Federalist Commerce</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>Charles C. Pinckney</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="5" t="n"/>
-      <c r="Y4" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence. Gain a story costing 4 or less from the exchange.</t>
-        </is>
-      </c>
-      <c r="Z4" s="5" t="inlineStr">
+          <t>The Twelfth Amendment</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Each paper draws a card.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>draw</t>
         </is>
       </c>
-      <c r="AA4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="6" t="inlineStr">
-        <is>
-          <t>The Twelfth Amendment</t>
-        </is>
-      </c>
-      <c r="AC4" s="6" t="inlineStr">
-        <is>
-          <t>Each paper draws a card.</t>
-        </is>
-      </c>
-      <c r="AD4" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence. Gain a story costing 4 or less from the exchange. Also +2 of the elected candidate's theme. Worth 3 prestige.</t>
-        </is>
+      <c r="L4" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -12129,104 +11873,46 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
+          <t>James Madison</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
           <t>The Embargo</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>2</v>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Charles C. Pinckney</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Free Trade and Sailors' Rights</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>James Madison</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>Charles C. Pinckney</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="5" t="n"/>
-      <c r="Y5" s="6" t="inlineStr">
-        <is>
-          <t>+4 influence.</t>
-        </is>
-      </c>
-      <c r="Z5" s="5" t="inlineStr">
+          <t>The Embargo</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Each paper discards the most expensive card in its hand.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>discard_dearest</t>
         </is>
       </c>
-      <c r="AA5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="6" t="inlineStr">
-        <is>
-          <t>The Embargo</t>
-        </is>
-      </c>
-      <c r="AC5" s="6" t="inlineStr">
-        <is>
-          <t>Each paper discards the most expensive card in its hand.</t>
-        </is>
-      </c>
-      <c r="AD5" s="6" t="inlineStr">
-        <is>
-          <t>+4 influence. Also +2 of the elected candidate's theme. Worth 3 prestige.</t>
-        </is>
+      <c r="L5" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -12243,104 +11929,46 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
+          <t>James Madison</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>Mr. Madison's War</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>2</v>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>DeWitt Clinton</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>The Peace Ticket</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>James Madison</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>DeWitt Clinton</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="5" t="n"/>
-      <c r="Y6" s="6" t="inlineStr">
-        <is>
-          <t>+1 influence for each different kind of card you play this turn.</t>
-        </is>
-      </c>
-      <c r="Z6" s="5" t="inlineStr">
+          <t>Impressment</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>scandal_leader</t>
         </is>
       </c>
-      <c r="AA6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="6" t="inlineStr">
-        <is>
-          <t>Impressment</t>
-        </is>
-      </c>
-      <c r="AC6" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="AD6" s="6" t="inlineStr">
-        <is>
-          <t>+1 influence for each different kind of card you play this turn. Also +2 of the elected candidate's theme. Worth 4 prestige.</t>
-        </is>
+      <c r="L6" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -12357,104 +11985,46 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
+          <t>James Monroe</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>The Era of Good Feelings</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Rufus King</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>The Last Federalist</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
           <t>Good Feelings</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>James Monroe</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>Rufus King</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="5" t="n"/>
-      <c r="Y7" s="6" t="inlineStr">
-        <is>
-          <t>Draw 3 cards.</t>
-        </is>
-      </c>
-      <c r="Z7" s="5" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Each paper destroys a Scandal in its hand or discard pile.</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>unscandal</t>
         </is>
       </c>
-      <c r="AA7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="6" t="inlineStr">
-        <is>
-          <t>Good Feelings</t>
-        </is>
-      </c>
-      <c r="AC7" s="6" t="inlineStr">
-        <is>
-          <t>Each paper destroys a Scandal in its hand or discard pile.</t>
-        </is>
-      </c>
-      <c r="AD7" s="6" t="inlineStr">
-        <is>
-          <t>Draw 3 cards. Also +2 of the elected candidate's theme. Worth 4 prestige.</t>
-        </is>
+      <c r="L7" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -12471,104 +12041,46 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
+          <t>John Quincy Adams</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>An Antislavery Diary</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>James Monroe</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
           <t>The Missouri Compromise</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>3</v>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>John Quincy Adams</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>James Monroe</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="5" t="n"/>
-      <c r="Y8" s="6" t="inlineStr">
-        <is>
-          <t>Destroy up to 2 cards in your hand or discard pile; draw a card for each.</t>
-        </is>
-      </c>
-      <c r="Z8" s="5" t="inlineStr">
+          <t>A Fire Bell in the Night</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards a card at random.</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>discard_leader</t>
         </is>
       </c>
-      <c r="AA8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="6" t="inlineStr">
-        <is>
-          <t>A Fire Bell in the Night</t>
-        </is>
-      </c>
-      <c r="AC8" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards a card at random.</t>
-        </is>
-      </c>
-      <c r="AD8" s="6" t="inlineStr">
-        <is>
-          <t>Destroy up to 2 cards in your hand or discard pile; draw a card for each. Also +3 of the elected candidate's theme. Worth 4 prestige.</t>
-        </is>
+      <c r="L8" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -12585,104 +12097,46 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
+          <t>John Quincy Adams</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
           <t>The Corrupt Bargain</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>3</v>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Jackson</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>The People's Choice</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>John Quincy Adams</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>Andrew Jackson</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="5" t="n"/>
-      <c r="Y9" s="6" t="inlineStr">
-        <is>
-          <t>Put up to 2 cards from your discard pile into your hand.</t>
-        </is>
-      </c>
-      <c r="Z9" s="5" t="inlineStr">
+          <t>The Corrupt Bargain</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>scandal_leader</t>
         </is>
       </c>
-      <c r="AA9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="6" t="inlineStr">
-        <is>
-          <t>The Corrupt Bargain</t>
-        </is>
-      </c>
-      <c r="AC9" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="AD9" s="6" t="inlineStr">
-        <is>
-          <t>Put up to 2 cards from your discard pile into your hand. Also +3 of the elected candidate's theme. Worth 4 prestige.</t>
-        </is>
+      <c r="L9" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -12699,104 +12153,46 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>The Tariff of Abominations</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>3</v>
+          <t>John Quincy Adams</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>The American System</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Jackson</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Jacksonian Democracy</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>John Quincy Adams</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>Andrew Jackson</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="5" t="n"/>
-      <c r="Y10" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence, draw a card.</t>
-        </is>
-      </c>
-      <c r="Z10" s="5" t="inlineStr">
+          <t>Mudslinging</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>scandal_leader</t>
         </is>
       </c>
-      <c r="AA10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="6" t="inlineStr">
-        <is>
-          <t>Mudslinging</t>
-        </is>
-      </c>
-      <c r="AC10" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="AD10" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence, draw a card. Also +3 of the elected candidate's theme. Worth 5 prestige.</t>
-        </is>
+      <c r="L10" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -12813,104 +12209,46 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
+          <t>Henry Clay</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>The Bank Recharter</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Jackson</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
           <t>The Bank War</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>3</v>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Henry Clay</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>Andrew Jackson</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="T11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="5" t="n"/>
-      <c r="Y11" s="6" t="inlineStr">
-        <is>
-          <t>Gain a story costing 6 or less from the exchange. Draw a card.</t>
-        </is>
-      </c>
-      <c r="Z11" s="5" t="inlineStr">
+          <t>The Veto</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>The exchange is swept and dealt afresh.</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>sweep</t>
         </is>
       </c>
-      <c r="AA11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="6" t="inlineStr">
-        <is>
-          <t>The Veto</t>
-        </is>
-      </c>
-      <c r="AC11" s="6" t="inlineStr">
-        <is>
-          <t>The exchange is swept and dealt afresh.</t>
-        </is>
-      </c>
-      <c r="AD11" s="6" t="inlineStr">
-        <is>
-          <t>Gain a story costing 6 or less from the exchange. Draw a card. Also +3 of the elected candidate's theme. Worth 5 prestige.</t>
-        </is>
+      <c r="L11" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -12927,104 +12265,46 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
+          <t>William Henry Harrison</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>The Whig Coalition</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Martin Van Buren</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>The Specie Circular</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>3</v>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>William Henry Harrison</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>Martin Van Buren</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="P12" s="5" t="n">
+          <t>The Panic of 1837</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="5" t="n"/>
-      <c r="Y12" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence, draw 2 cards.</t>
-        </is>
-      </c>
-      <c r="Z12" s="5" t="inlineStr">
-        <is>
-          <t>discard_leader</t>
-        </is>
-      </c>
-      <c r="AA12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB12" s="6" t="inlineStr">
-        <is>
-          <t>The Panic of 1837</t>
-        </is>
-      </c>
-      <c r="AC12" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
-        </is>
-      </c>
-      <c r="AD12" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence, draw 2 cards. Also +3 of the elected candidate's theme. Worth 5 prestige.</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -13041,104 +12321,46 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
+          <t>William Henry Harrison</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
           <t>Log Cabin and Hard Cider</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>3</v>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Martin Van Buren</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>The Independent Treasury</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>William Henry Harrison</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>Martin Van Buren</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="5" t="n"/>
-      <c r="Y13" s="6" t="inlineStr">
-        <is>
-          <t>+4 influence.</t>
-        </is>
-      </c>
-      <c r="Z13" s="5" t="inlineStr">
+          <t>Tippecanoe and Tyler Too</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Each paper draws a card.</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>draw</t>
         </is>
       </c>
-      <c r="AA13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="6" t="inlineStr">
-        <is>
-          <t>Tippecanoe and Tyler Too</t>
-        </is>
-      </c>
-      <c r="AC13" s="6" t="inlineStr">
-        <is>
-          <t>Each paper draws a card.</t>
-        </is>
-      </c>
-      <c r="AD13" s="6" t="inlineStr">
-        <is>
-          <t>+4 influence. Also +3 of the elected candidate's theme. Worth 5 prestige.</t>
-        </is>
+      <c r="L13" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -13155,104 +12377,46 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
+          <t>Henry Clay</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>The Raleigh Letter</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>James K. Polk</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
           <t>Manifest Destiny</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5" t="n">
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Fifty-four Forty</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the fewest offices draws 2 cards.</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>draw_fewest</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Henry Clay</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>James K. Polk</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="W14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="5" t="n"/>
-      <c r="Y14" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence. Look at the top 3 stories of the main deck; put one into your hand, the rest on the bottom.</t>
-        </is>
-      </c>
-      <c r="Z14" s="5" t="inlineStr">
-        <is>
-          <t>draw_fewest</t>
-        </is>
-      </c>
-      <c r="AA14" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB14" s="6" t="inlineStr">
-        <is>
-          <t>Fifty-four Forty</t>
-        </is>
-      </c>
-      <c r="AC14" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the fewest offices draws 2 cards.</t>
-        </is>
-      </c>
-      <c r="AD14" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence. Look at the top 3 stories of the main deck; put one into your hand, the rest on the bottom. Also +4 of the elected candidate's theme. Worth 6 prestige.</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -13269,104 +12433,46 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>The Free Soil Revolt</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>4</v>
+          <t>Zachary Taylor</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Old Rough and Ready</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Lewis Cass</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Popular Sovereignty</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Zachary Taylor</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>Lewis Cass</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="5" t="n"/>
-      <c r="Y15" s="6" t="inlineStr">
-        <is>
-          <t>+1 influence for each different kind of card you play this turn. Draw a card.</t>
-        </is>
-      </c>
-      <c r="Z15" s="5" t="inlineStr">
+          <t>The Wilmot Proviso</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Each paper destroys the cheapest card in its hand.</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>destroy_cheapest</t>
         </is>
       </c>
-      <c r="AA15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="6" t="inlineStr">
-        <is>
-          <t>The Wilmot Proviso</t>
-        </is>
-      </c>
-      <c r="AC15" s="6" t="inlineStr">
-        <is>
-          <t>Each paper destroys the cheapest card in its hand.</t>
-        </is>
-      </c>
-      <c r="AD15" s="6" t="inlineStr">
-        <is>
-          <t>+1 influence for each different kind of card you play this turn. Draw a card. Also +4 of the elected candidate's theme. Worth 6 prestige.</t>
-        </is>
+      <c r="L15" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -13383,104 +12489,46 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
+          <t>Winfield Scott</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Old Fuss and Feathers</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Franklin Pierce</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
           <t>The Compromise of 1850</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>4</v>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>Winfield Scott</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>Franklin Pierce</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="5" t="n"/>
-      <c r="Y16" s="6" t="inlineStr">
-        <is>
-          <t>Destroy up to 3 cards in your hand or discard pile; draw a card for each.</t>
-        </is>
-      </c>
-      <c r="Z16" s="5" t="inlineStr">
+          <t>The Fugitive Slave Act</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>scandal_leader</t>
         </is>
       </c>
-      <c r="AA16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="6" t="inlineStr">
-        <is>
-          <t>The Fugitive Slave Act</t>
-        </is>
-      </c>
-      <c r="AC16" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="AD16" s="6" t="inlineStr">
-        <is>
-          <t>Destroy up to 3 cards in your hand or discard pile; draw a card for each. Also +4 of the elected candidate's theme. Worth 6 prestige.</t>
-        </is>
+      <c r="L16" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -13497,108 +12545,46 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
+          <t>John C. Fremont</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Free Soil, Free Men, Fremont</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>James Buchanan</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
           <t>Bleeding Kansas</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>4</v>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>John C. Fremont</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>James Buchanan</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="5" t="inlineStr">
-        <is>
-          <t>scandal</t>
-        </is>
-      </c>
-      <c r="Y17" s="6" t="inlineStr">
-        <is>
-          <t>+5 influence. Attack: each rival paper gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="Z17" s="5" t="inlineStr">
+          <t>Bleeding Kansas</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>discard_leader</t>
         </is>
       </c>
-      <c r="AA17" s="5" t="n">
+      <c r="L17" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="AB17" s="6" t="inlineStr">
-        <is>
-          <t>Bleeding Kansas</t>
-        </is>
-      </c>
-      <c r="AC17" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
-        </is>
-      </c>
-      <c r="AD17" s="6" t="inlineStr">
-        <is>
-          <t>+5 influence. Attack: each rival paper gains a Scandal. Also +4 of the elected candidate's theme. Worth 6 prestige.</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -13615,113 +12601,2762 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Secession Winter</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>4</v>
+          <t>Abraham Lincoln</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>A House Divided</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Stephen A. Douglas</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>The Little Giant</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>Abraham Lincoln</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>Stephen A. Douglas</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="5" t="n"/>
-      <c r="Y18" s="6" t="inlineStr">
-        <is>
-          <t>The last election: the game ends after this turn. Worth 1 prestige for each election card you hold, this one included.</t>
-        </is>
-      </c>
-      <c r="Z18" s="5" t="inlineStr">
+          <t>Secession</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Each paper destroys the cheapest card in its hand.</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>destroy_cheapest</t>
         </is>
       </c>
-      <c r="AA18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="6" t="inlineStr">
-        <is>
-          <t>Secession</t>
-        </is>
-      </c>
-      <c r="AC18" s="6" t="inlineStr">
-        <is>
-          <t>Each paper destroys the cheapest card in its hand.</t>
-        </is>
-      </c>
-      <c r="AD18" s="6" t="inlineStr">
-        <is>
-          <t>The last election: the game ends after this turn. Worth 1 prestige for each election card you hold, this one included.</t>
-        </is>
+      <c r="L18" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD18"/>
+  <autoFilter ref="A1:L18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="55" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>theme</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>card_name</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Prestige</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Prestige per office</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Influence (plain)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Candidate-theme influence</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Destroy</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Draw per destroyed</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Gain (cost up to)</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Recover</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Per kind played</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Look at top</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Stays in play</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>1796-nation</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>1796</v>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>John Adams</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>The Federalist Administration</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5" t="n"/>
+      <c r="U2" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence, draw a card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>1796-states</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>1796</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>The Republican Societies</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="5" t="n"/>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>Draw 2 cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>1800-nation</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>John Adams</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>The Alien and Sedition Acts</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>discard</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence. Attack: each rival paper discards a card at random.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1800-states</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>The Revolution of 1800</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence, draw 2 cards, then you may destroy a card in your hand or discard pile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1804-nation</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1804</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>The Louisiana Purchase</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence. Gain a story costing 4 or less from the exchange.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>1804-states</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1804</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Charles C. Pinckney</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Federalist Commerce</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence, then you may destroy a card in your hand or discard pile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1808-nation</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1808</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>James Madison</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>The Embargo</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="6" t="inlineStr">
+        <is>
+          <t>+4 influence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>1808-states</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1808</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Charles C. Pinckney</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Free Trade and Sailors' Rights</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="6" t="inlineStr">
+        <is>
+          <t>Gain a story costing 5 or less from the exchange.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>1812-nation</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1812</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>James Madison</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Mr. Madison's War</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="6" t="inlineStr">
+        <is>
+          <t>+1 influence for each different kind of card you play this turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>1812-states</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1812</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>DeWitt Clinton</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>The Peace Ticket</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence, draw 2 cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>1816-nation</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1816</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>James Monroe</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>The Era of Good Feelings</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="6" t="inlineStr">
+        <is>
+          <t>Draw 3 cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>1816-states</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1816</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Rufus King</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>The Last Federalist</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence. Put a card from your discard pile into your hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>1820-nation</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1820</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>John Quincy Adams</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>An Antislavery Diary</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>+1 influence. Look at the top 3 stories of the main deck; put one into your hand, the rest on the bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>1820-states</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1820</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>James Monroe</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>The Missouri Compromise</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>Destroy up to 2 cards in your hand or discard pile; draw a card for each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>1824-nation</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1824</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>John Quincy Adams</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>The Corrupt Bargain</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>Put up to 2 cards from your discard pile into your hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>1824-states</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1824</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Jackson</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>The People's Choice</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="6" t="inlineStr">
+        <is>
+          <t>+4 influence, draw a card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>1828-nation</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>John Quincy Adams</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>The American System</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="6" t="inlineStr">
+        <is>
+          <t>Gain a story costing 5 or less from the exchange. Draw a card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>1828-states</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Jackson</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Jacksonian Democracy</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence, draw a card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>1832-nation</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1832</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Henry Clay</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>The Bank Recharter</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence. Gain a story costing 4 or less from the exchange.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>1832-states</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1832</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Jackson</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>The Bank War</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="6" t="inlineStr">
+        <is>
+          <t>Gain a story costing 6 or less from the exchange. Draw a card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>1836-nation</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>William Henry Harrison</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>The Whig Coalition</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="5" t="n"/>
+      <c r="U22" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence, and +1 for each different kind of card you play this turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>1836-states</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Martin Van Buren</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>The Specie Circular</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="5" t="n"/>
+      <c r="U23" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence, draw 2 cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>1840-nation</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1840</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>William Henry Harrison</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Log Cabin and Hard Cider</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>+4 influence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>1840-states</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1840</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Martin Van Buren</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>The Independent Treasury</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence. Destroy up to 2 cards in your hand or discard pile; draw a card for each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>1844-nation</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1844</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Henry Clay</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>The Raleigh Letter</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="5" t="n"/>
+      <c r="U26" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence. Put a card from your discard pile into your hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>1844-states</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1844</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>James K. Polk</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Manifest Destiny</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="5" t="n"/>
+      <c r="U27" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence. Look at the top 3 stories of the main deck; put one into your hand, the rest on the bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>1848-nation</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1848</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Zachary Taylor</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Old Rough and Ready</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>discard</t>
+        </is>
+      </c>
+      <c r="U28" s="6" t="inlineStr">
+        <is>
+          <t>+4 influence. Attack: each rival paper discards a card at random.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>1848-states</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1848</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Lewis Cass</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Popular Sovereignty</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="5" t="n"/>
+      <c r="U29" s="6" t="inlineStr">
+        <is>
+          <t>+1 influence for each different kind of card you play this turn. Draw a card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>1852-nation</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1852</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Winfield Scott</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Old Fuss and Feathers</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="5" t="n"/>
+      <c r="U30" s="6" t="inlineStr">
+        <is>
+          <t>+5 influence, draw a card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>1852-states</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>1852</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Franklin Pierce</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>The Compromise of 1850</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="5" t="n"/>
+      <c r="U31" s="6" t="inlineStr">
+        <is>
+          <t>Destroy up to 3 cards in your hand or discard pile; draw a card for each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>1856-nation</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>1856</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>John C. Fremont</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Free Soil, Free Men, Fremont</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="5" t="n"/>
+      <c r="U32" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence, draw 2 cards, then you may destroy a card in your hand or discard pile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>1856-states</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>1856</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>James Buchanan</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Bleeding Kansas</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="5" t="inlineStr">
+        <is>
+          <t>scandal</t>
+        </is>
+      </c>
+      <c r="U33" s="6" t="inlineStr">
+        <is>
+          <t>+5 influence. Attack: each rival paper gains a Scandal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>1860-nation</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>1860</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Abraham Lincoln</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>A House Divided</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="5" t="n"/>
+      <c r="U34" s="6" t="inlineStr">
+        <is>
+          <t>The last election: the game ends after this turn. Worth 1 prestige for each election card you hold, this one included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>1860-states</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1860</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Stephen A. Douglas</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>The Little Giant</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="5" t="n"/>
+      <c r="U35" s="6" t="inlineStr">
+        <is>
+          <t>The last election: the game ends after this turn. Worth 2 prestige, plus 1 for each election card you hold, this one included.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:U35"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14032,7 +15667,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14378,11 +16013,11 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Elections: fixed prestige on the 17 cards (1860 is worth 1 per office held, not counted)</t>
+          <t>Candidates: fixed prestige on all 34 cards (1860 is also worth 1 per office held)</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <f>SUM(Elections!$E$2:$E$18)</f>
+        <f>SUM(Candidates!$H$2:$H$35)</f>
         <v/>
       </c>
       <c r="C19" s="2" t="n"/>

--- a/docs/fourth-estate-cards.xlsx
+++ b/docs/fourth-estate-cards.xlsx
@@ -10,15 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elections" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newspapers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newspapers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stories'!$A$1:$AC$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Elections'!$A$1:$L$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Candidates'!$A$1:$U$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Newspapers'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Elections'!$A$1:$AA$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Newspapers'!$A$1:$F$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -56,7 +54,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +64,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00143138"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -93,6 +96,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -461,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -515,14 +524,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Elections -- the 17 elections: the two candidates, history's choice, and the First Appearance event when the campaign opens.</t>
+          <t>Elections -- 34 election cards, one per candidate (two rows per year): his card's prestige and power, one column per effect,</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Candidates -- the 34 candidates, each his own card: theme, threshold, the card's prestige and its power, one column per effect.</t>
+          <t xml:space="preserve">             and the First Appearance event that opens that year's campaign (the same on both rows).</t>
         </is>
       </c>
     </row>
@@ -612,73 +621,63 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>nation / states = the two candidates (their cards are on the Candidates sheet); historical_winner = history's choice (2 cheaper);</t>
+          <t>key = year-side (nation or states); History's choice = yes on the candidate history elected (2 cheaper to elect);</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>First Appearance = what happens to every paper as the campaign opens; fa_kind = which event: discard, discard_leader, discard_dearest,</t>
+          <t>theme = the influence that counts toward him; threshold = influence needed to elect him; card_name = the card his Patron gains;</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>destroy_cheapest, draw, draw_fewest, scandal, scandal_leader, unscandal, sweep; First Appearance: how many = its number.</t>
+          <t>Prestige = the card's prestige; Prestige per office = prestige for each election card its holder owns (1860);</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>the power when played: Influence (plain); Candidate-theme influence (his theme); Draw; Destroy (up to N cards from hand or discard);</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Candidates columns</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Draw per destroyed (1 = draw a card for each); Gain (cost up to) a story from the exchange; Recover (cards from discard to hand);</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>key = year-side; theme = the influence that counts toward him; threshold = influence needed to elect him; card_name = his card;</t>
+          <t>Per kind played (+N per different kind of card played this turn); Look at top (look at the top N of the main deck, keep 1);</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Prestige = the card's prestige; Prestige per office = prestige for each election card its holder owns (1860);</t>
+          <t>Stays in play (+N each turn; none now); Attack (discard or scandal, every rival); Power = the card's text.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>the power when played: Influence (plain); Candidate-theme influence (his theme); Draw; Destroy (up to N cards from hand or discard);</t>
+          <t>First Appearance = what happens to every paper as that year's campaign opens; fa_kind = which event: discard, discard_leader,</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Draw per destroyed (1 = draw a card for each); Gain (cost up to) a story from the exchange; Recover (cards from discard to hand);</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Per kind played (+N per different kind of card played this turn); Look at top (look at the top N of the main deck, keep 1);</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Stays in play (+N each turn; none now); Attack (discard or scandal, every rival); Power = the card's text.</t>
+          <t>discard_dearest, destroy_cheapest, draw, draw_fewest, scandal, scandal_leader, unscandal, sweep; First Appearance: how many = its number.</t>
         </is>
       </c>
     </row>
@@ -11624,27 +11623,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="55" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="45" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>space</t>
+          <t>key</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
@@ -11659,53 +11673,130 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>nation</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>nation card</t>
+          <t>candidate</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
-          <t>states</t>
+          <t>History's choice</t>
         </is>
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>states card</t>
+          <t>theme</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>historical_winner</t>
+          <t>threshold</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
+          <t>card_name</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Prestige</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Prestige per office</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Influence (plain)</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Candidate-theme influence</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Destroy</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Draw per destroyed</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Gain (cost up to)</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Recover</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Per kind played</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Look at top</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Stays in play</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
           <t>fa_name</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>First Appearance</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>fa_kind</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>First Appearance: how many</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>1</v>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>1796-nation</t>
+        </is>
       </c>
       <c r="B2" s="5" t="n">
         <v>1796</v>
@@ -11715,3648 +11806,3421 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>John Adams</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>The Federalist Administration</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="J2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="n"/>
+      <c r="W2" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence, draw a card.</t>
+        </is>
+      </c>
+      <c r="X2" s="6" t="n"/>
+      <c r="Y2" s="6" t="n"/>
+      <c r="Z2" s="5" t="n"/>
+      <c r="AA2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>1796-states</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>1796</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Thomas Jefferson</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>The Republican Societies</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="J3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5" t="n"/>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>Draw 2 cards.</t>
+        </is>
+      </c>
+      <c r="X3" s="6" t="n"/>
+      <c r="Y3" s="6" t="n"/>
+      <c r="Z3" s="5" t="n"/>
+      <c r="AA3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1800-nation</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>nation</t>
         </is>
       </c>
-      <c r="I2" s="6" t="n"/>
-      <c r="J2" s="6" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>John Adams</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>The Alien and Sedition Acts</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="M4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="7" t="inlineStr">
+        <is>
+          <t>discard</t>
+        </is>
+      </c>
+      <c r="W4" s="8" t="inlineStr">
+        <is>
+          <t>+2 influence. Attack: each rival paper discards a card at random.</t>
+        </is>
+      </c>
+      <c r="X4" s="8" t="inlineStr">
+        <is>
+          <t>The Sedition Act</t>
+        </is>
+      </c>
+      <c r="Y4" s="8" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards a card at random.</t>
+        </is>
+      </c>
+      <c r="Z4" s="7" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
+      </c>
+      <c r="AA4" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>1800-states</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>John Adams</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>The Alien and Sedition Acts</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Thomas Jefferson</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>The Revolution of 1800</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="7" t="n"/>
+      <c r="W5" s="8" t="inlineStr">
+        <is>
+          <t>+2 influence, draw 2 cards, then you may destroy a card in your hand or discard pile.</t>
+        </is>
+      </c>
+      <c r="X5" s="8" t="inlineStr">
+        <is>
+          <t>The Sedition Act</t>
+        </is>
+      </c>
+      <c r="Y5" s="8" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards a card at random.</t>
+        </is>
+      </c>
+      <c r="Z5" s="7" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
+      </c>
+      <c r="AA5" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1804-nation</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1804</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>The Louisiana Purchase</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence. Gain a story costing 4 or less from the exchange.</t>
+        </is>
+      </c>
+      <c r="X6" s="6" t="inlineStr">
+        <is>
+          <t>The Twelfth Amendment</t>
+        </is>
+      </c>
+      <c r="Y6" s="6" t="inlineStr">
+        <is>
+          <t>Each paper draws a card.</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="AA6" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>1804-states</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1804</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>states</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>The Sedition Act</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Charles C. Pinckney</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Federalist Commerce</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence, then you may destroy a card in your hand or discard pile.</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr">
+        <is>
+          <t>The Twelfth Amendment</t>
+        </is>
+      </c>
+      <c r="Y7" s="6" t="inlineStr">
+        <is>
+          <t>Each paper draws a card.</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="AA7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>1808-nation</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>1808</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>James Madison</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>The Embargo</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="7" t="n"/>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>+4 influence.</t>
+        </is>
+      </c>
+      <c r="X8" s="8" t="inlineStr">
+        <is>
+          <t>The Embargo</t>
+        </is>
+      </c>
+      <c r="Y8" s="8" t="inlineStr">
+        <is>
+          <t>Each paper discards the most expensive card in its hand.</t>
+        </is>
+      </c>
+      <c r="Z8" s="7" t="inlineStr">
+        <is>
+          <t>discard_dearest</t>
+        </is>
+      </c>
+      <c r="AA8" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>1808-states</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>1808</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Charles C. Pinckney</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Free Trade and Sailors' Rights</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="7" t="n"/>
+      <c r="W9" s="8" t="inlineStr">
+        <is>
+          <t>Gain a story costing 5 or less from the exchange.</t>
+        </is>
+      </c>
+      <c r="X9" s="8" t="inlineStr">
+        <is>
+          <t>The Embargo</t>
+        </is>
+      </c>
+      <c r="Y9" s="8" t="inlineStr">
+        <is>
+          <t>Each paper discards the most expensive card in its hand.</t>
+        </is>
+      </c>
+      <c r="Z9" s="7" t="inlineStr">
+        <is>
+          <t>discard_dearest</t>
+        </is>
+      </c>
+      <c r="AA9" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>1812-nation</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1812</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>James Madison</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Mr. Madison's War</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="6" t="inlineStr">
+        <is>
+          <t>+1 influence for each different kind of card you play this turn.</t>
+        </is>
+      </c>
+      <c r="X10" s="6" t="inlineStr">
+        <is>
+          <t>Impressment</t>
+        </is>
+      </c>
+      <c r="Y10" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="Z10" s="5" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
+      </c>
+      <c r="AA10" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>1812-states</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1812</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>DeWitt Clinton</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>The Peace Ticket</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence, draw 2 cards.</t>
+        </is>
+      </c>
+      <c r="X11" s="6" t="inlineStr">
+        <is>
+          <t>Impressment</t>
+        </is>
+      </c>
+      <c r="Y11" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="Z11" s="5" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
+      </c>
+      <c r="AA11" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>1816-nation</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>1816</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>James Monroe</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>The Era of Good Feelings</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="7" t="n"/>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>Draw 3 cards.</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>Good Feelings</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>Each paper destroys a Scandal in its hand or discard pile.</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
+        <is>
+          <t>unscandal</t>
+        </is>
+      </c>
+      <c r="AA12" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>1816-states</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>1816</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Rufus King</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>The Last Federalist</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="7" t="n"/>
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>+2 influence. Put a card from your discard pile into your hand.</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>Good Feelings</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>Each paper destroys a Scandal in its hand or discard pile.</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
+        <is>
+          <t>unscandal</t>
+        </is>
+      </c>
+      <c r="AA13" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>1820-nation</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1820</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>John Quincy Adams</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>An Antislavery Diary</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5" t="n"/>
+      <c r="W14" s="6" t="inlineStr">
+        <is>
+          <t>+1 influence. Look at the top 3 stories of the main deck; put one into your hand, the rest on the bottom.</t>
+        </is>
+      </c>
+      <c r="X14" s="6" t="inlineStr">
+        <is>
+          <t>A Fire Bell in the Night</t>
+        </is>
+      </c>
+      <c r="Y14" s="6" t="inlineStr">
         <is>
           <t>The paper (or papers) holding the most offices discards a card at random.</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="Z14" s="5" t="inlineStr">
         <is>
           <t>discard_leader</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="AA14" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>1820-states</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1820</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>James Monroe</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>The Missouri Compromise</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>1804</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>The Louisiana Purchase</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Charles C. Pinckney</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Federalist Commerce</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="N15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="6" t="inlineStr">
+        <is>
+          <t>Destroy up to 2 cards in your hand or discard pile; draw a card for each.</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
+        <is>
+          <t>A Fire Bell in the Night</t>
+        </is>
+      </c>
+      <c r="Y15" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards a card at random.</t>
+        </is>
+      </c>
+      <c r="Z15" s="5" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
+      </c>
+      <c r="AA15" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>1824-nation</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>1824</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>nation</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>The Twelfth Amendment</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>John Quincy Adams</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>The Corrupt Bargain</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="7" t="n"/>
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>Put up to 2 cards from your discard pile into your hand.</t>
+        </is>
+      </c>
+      <c r="X16" s="8" t="inlineStr">
+        <is>
+          <t>The Corrupt Bargain</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
+      </c>
+      <c r="AA16" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>1824-states</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>1824</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Andrew Jackson</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>The People's Choice</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="7" t="n"/>
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>+4 influence, draw a card.</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t>The Corrupt Bargain</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
+      </c>
+      <c r="AA17" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>1828-nation</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>John Quincy Adams</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>The American System</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="6" t="inlineStr">
+        <is>
+          <t>Gain a story costing 5 or less from the exchange. Draw a card.</t>
+        </is>
+      </c>
+      <c r="X18" s="6" t="inlineStr">
+        <is>
+          <t>Mudslinging</t>
+        </is>
+      </c>
+      <c r="Y18" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="Z18" s="5" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
+      </c>
+      <c r="AA18" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>1828-states</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Jackson</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Jacksonian Democracy</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5" t="n"/>
+      <c r="W19" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence, draw a card.</t>
+        </is>
+      </c>
+      <c r="X19" s="6" t="inlineStr">
+        <is>
+          <t>Mudslinging</t>
+        </is>
+      </c>
+      <c r="Y19" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="Z19" s="5" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
+      </c>
+      <c r="AA19" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>1832-nation</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>1832</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Henry Clay</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>The Bank Recharter</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="7" t="n"/>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>+3 influence. Gain a story costing 4 or less from the exchange.</t>
+        </is>
+      </c>
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t>The Veto</t>
+        </is>
+      </c>
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>The exchange is swept and dealt afresh.</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
+        <is>
+          <t>sweep</t>
+        </is>
+      </c>
+      <c r="AA20" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>1832-states</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>1832</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Andrew Jackson</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>The Bank War</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="7" t="n"/>
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t>Gain a story costing 6 or less from the exchange. Draw a card.</t>
+        </is>
+      </c>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t>The Veto</t>
+        </is>
+      </c>
+      <c r="Y21" s="8" t="inlineStr">
+        <is>
+          <t>The exchange is swept and dealt afresh.</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
+        <is>
+          <t>sweep</t>
+        </is>
+      </c>
+      <c r="AA21" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>1836-nation</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>William Henry Harrison</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>The Whig Coalition</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence, and +1 for each different kind of card you play this turn.</t>
+        </is>
+      </c>
+      <c r="X22" s="6" t="inlineStr">
+        <is>
+          <t>The Panic of 1837</t>
+        </is>
+      </c>
+      <c r="Y22" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
+        </is>
+      </c>
+      <c r="Z22" s="5" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
+      </c>
+      <c r="AA22" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>1836-states</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Martin Van Buren</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>The Specie Circular</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="5" t="n"/>
+      <c r="W23" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence, draw 2 cards.</t>
+        </is>
+      </c>
+      <c r="X23" s="6" t="inlineStr">
+        <is>
+          <t>The Panic of 1837</t>
+        </is>
+      </c>
+      <c r="Y23" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
+        </is>
+      </c>
+      <c r="Z23" s="5" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
+      </c>
+      <c r="AA23" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>1840-nation</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>1840</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>William Henry Harrison</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Log Cabin and Hard Cider</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="7" t="n"/>
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t>+4 influence.</t>
+        </is>
+      </c>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t>Tippecanoe and Tyler Too</t>
+        </is>
+      </c>
+      <c r="Y24" s="8" t="inlineStr">
         <is>
           <t>Each paper draws a card.</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="Z24" s="7" t="inlineStr">
         <is>
           <t>draw</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="AA24" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>1840-states</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>1840</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Martin Van Buren</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>The Independent Treasury</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="7" t="n"/>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t>+2 influence. Destroy up to 2 cards in your hand or discard pile; draw a card for each.</t>
+        </is>
+      </c>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t>Tippecanoe and Tyler Too</t>
+        </is>
+      </c>
+      <c r="Y25" s="8" t="inlineStr">
+        <is>
+          <t>Each paper draws a card.</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="AA25" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>1844-nation</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1844</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Henry Clay</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>The Raleigh Letter</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>1808</v>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>James Madison</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>The Embargo</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Charles C. Pinckney</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Free Trade and Sailors' Rights</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="N26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="5" t="n"/>
+      <c r="W26" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence. Put a card from your discard pile into your hand.</t>
+        </is>
+      </c>
+      <c r="X26" s="6" t="inlineStr">
+        <is>
+          <t>Fifty-four Forty</t>
+        </is>
+      </c>
+      <c r="Y26" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the fewest offices draws 2 cards.</t>
+        </is>
+      </c>
+      <c r="Z26" s="5" t="inlineStr">
+        <is>
+          <t>draw_fewest</t>
+        </is>
+      </c>
+      <c r="AA26" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>1844-states</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1844</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>James K. Polk</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Manifest Destiny</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="5" t="n"/>
+      <c r="W27" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence. Look at the top 3 stories of the main deck; put one into your hand, the rest on the bottom.</t>
+        </is>
+      </c>
+      <c r="X27" s="6" t="inlineStr">
+        <is>
+          <t>Fifty-four Forty</t>
+        </is>
+      </c>
+      <c r="Y27" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the fewest offices draws 2 cards.</t>
+        </is>
+      </c>
+      <c r="Z27" s="5" t="inlineStr">
+        <is>
+          <t>draw_fewest</t>
+        </is>
+      </c>
+      <c r="AA27" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>1848-nation</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>1848</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>nation</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>The Embargo</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Each paper discards the most expensive card in its hand.</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>discard_dearest</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Zachary Taylor</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Old Rough and Ready</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="7" t="inlineStr">
+        <is>
+          <t>discard</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
+        <is>
+          <t>+4 influence. Attack: each rival paper discards a card at random.</t>
+        </is>
+      </c>
+      <c r="X28" s="8" t="inlineStr">
+        <is>
+          <t>The Wilmot Proviso</t>
+        </is>
+      </c>
+      <c r="Y28" s="8" t="inlineStr">
+        <is>
+          <t>Each paper destroys the cheapest card in its hand.</t>
+        </is>
+      </c>
+      <c r="Z28" s="7" t="inlineStr">
+        <is>
+          <t>destroy_cheapest</t>
+        </is>
+      </c>
+      <c r="AA28" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>1848-states</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>1848</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Lewis Cass</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>Popular Sovereignty</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="7" t="n"/>
+      <c r="W29" s="8" t="inlineStr">
+        <is>
+          <t>+1 influence for each different kind of card you play this turn. Draw a card.</t>
+        </is>
+      </c>
+      <c r="X29" s="8" t="inlineStr">
+        <is>
+          <t>The Wilmot Proviso</t>
+        </is>
+      </c>
+      <c r="Y29" s="8" t="inlineStr">
+        <is>
+          <t>Each paper destroys the cheapest card in its hand.</t>
+        </is>
+      </c>
+      <c r="Z29" s="7" t="inlineStr">
+        <is>
+          <t>destroy_cheapest</t>
+        </is>
+      </c>
+      <c r="AA29" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>1852-nation</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1852</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>nation</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Winfield Scott</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Old Fuss and Feathers</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>1812</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>James Madison</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Mr. Madison's War</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>DeWitt Clinton</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>The Peace Ticket</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="M30" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="5" t="n"/>
+      <c r="W30" s="6" t="inlineStr">
+        <is>
+          <t>+5 influence, draw a card.</t>
+        </is>
+      </c>
+      <c r="X30" s="6" t="inlineStr">
+        <is>
+          <t>The Fugitive Slave Act</t>
+        </is>
+      </c>
+      <c r="Y30" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="Z30" s="5" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
+      </c>
+      <c r="AA30" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>1852-states</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>1852</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Franklin Pierce</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>The Compromise of 1850</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="5" t="n"/>
+      <c r="W31" s="6" t="inlineStr">
+        <is>
+          <t>Destroy up to 3 cards in your hand or discard pile; draw a card for each.</t>
+        </is>
+      </c>
+      <c r="X31" s="6" t="inlineStr">
+        <is>
+          <t>The Fugitive Slave Act</t>
+        </is>
+      </c>
+      <c r="Y31" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="Z31" s="5" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
+      </c>
+      <c r="AA31" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>1856-nation</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>1856</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>nation</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Impressment</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>scandal_leader</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>John C. Fremont</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>Free Soil, Free Men, Fremont</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>1816</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>James Monroe</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>The Era of Good Feelings</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Rufus King</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>The Last Federalist</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="K32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="7" t="n"/>
+      <c r="W32" s="8" t="inlineStr">
+        <is>
+          <t>+3 influence, draw 2 cards, then you may destroy a card in your hand or discard pile.</t>
+        </is>
+      </c>
+      <c r="X32" s="8" t="inlineStr">
+        <is>
+          <t>Bleeding Kansas</t>
+        </is>
+      </c>
+      <c r="Y32" s="8" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
+        </is>
+      </c>
+      <c r="Z32" s="7" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
+      </c>
+      <c r="AA32" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>1856-states</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>1856</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>states</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>James Buchanan</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Bleeding Kansas</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="7" t="inlineStr">
+        <is>
+          <t>scandal</t>
+        </is>
+      </c>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t>+5 influence. Attack: each rival paper gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="X33" s="8" t="inlineStr">
+        <is>
+          <t>Bleeding Kansas</t>
+        </is>
+      </c>
+      <c r="Y33" s="8" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
+        </is>
+      </c>
+      <c r="Z33" s="7" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
+      </c>
+      <c r="AA33" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>1860-nation</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>1860</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>nation</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Good Feelings</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Each paper destroys a Scandal in its hand or discard pile.</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>unscandal</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>1820</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>John Quincy Adams</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>An Antislavery Diary</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>James Monroe</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>The Missouri Compromise</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Abraham Lincoln</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Political</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>A House Divided</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="5" t="n"/>
+      <c r="W34" s="6" t="inlineStr">
+        <is>
+          <t>The last election: the game ends after this turn. Worth 1 prestige for each election card you hold, this one included.</t>
+        </is>
+      </c>
+      <c r="X34" s="6" t="inlineStr">
+        <is>
+          <t>Secession</t>
+        </is>
+      </c>
+      <c r="Y34" s="6" t="inlineStr">
+        <is>
+          <t>Each paper destroys the cheapest card in its hand.</t>
+        </is>
+      </c>
+      <c r="Z34" s="5" t="inlineStr">
+        <is>
+          <t>destroy_cheapest</t>
+        </is>
+      </c>
+      <c r="AA34" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>1860-states</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1860</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>states</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>A Fire Bell in the Night</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards a card at random.</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>discard_leader</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>1824</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>John Quincy Adams</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>The Corrupt Bargain</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Andrew Jackson</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>The People's Choice</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>The Corrupt Bargain</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>scandal_leader</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>1828</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>John Quincy Adams</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>The American System</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Andrew Jackson</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Jacksonian Democracy</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Mudslinging</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>scandal_leader</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>1832</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Henry Clay</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>The Bank Recharter</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Andrew Jackson</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>The Bank War</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>The Veto</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>The exchange is swept and dealt afresh.</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>sweep</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>1836</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>William Henry Harrison</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>The Whig Coalition</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Martin Van Buren</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>The Specie Circular</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>The Panic of 1837</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>discard_leader</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="n">
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Stephen A. Douglas</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>The Little Giant</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>1840</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>William Henry Harrison</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Log Cabin and Hard Cider</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Martin Van Buren</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>The Independent Treasury</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Tippecanoe and Tyler Too</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Each paper draws a card.</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>1844</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Henry Clay</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>The Raleigh Letter</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>James K. Polk</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>Manifest Destiny</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Fifty-four Forty</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the fewest offices draws 2 cards.</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>draw_fewest</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>1848</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Zachary Taylor</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Old Rough and Ready</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Lewis Cass</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Popular Sovereignty</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>The Wilmot Proviso</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="K35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="5" t="n"/>
+      <c r="W35" s="6" t="inlineStr">
+        <is>
+          <t>The last election: the game ends after this turn. Worth 2 prestige, plus 1 for each election card you hold, this one included.</t>
+        </is>
+      </c>
+      <c r="X35" s="6" t="inlineStr">
+        <is>
+          <t>Secession</t>
+        </is>
+      </c>
+      <c r="Y35" s="6" t="inlineStr">
         <is>
           <t>Each paper destroys the cheapest card in its hand.</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="Z35" s="5" t="inlineStr">
         <is>
           <t>destroy_cheapest</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>1852</v>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Winfield Scott</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Old Fuss and Feathers</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Franklin Pierce</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>The Compromise of 1850</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>The Fugitive Slave Act</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>scandal_leader</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1856</v>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>John C. Fremont</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Free Soil, Free Men, Fremont</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>James Buchanan</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>Bleeding Kansas</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Bleeding Kansas</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>discard_leader</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>1860</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>III</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Abraham Lincoln</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>A House Divided</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Stephen A. Douglas</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>The Little Giant</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Secession</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Each paper destroys the cheapest card in its hand.</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>destroy_cheapest</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="n">
+      <c r="AA35" s="5" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L18"/>
+  <autoFilter ref="A1:AA35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="55" customWidth="1" min="21" max="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>side</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>theme</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>card_name</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Prestige</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Prestige per office</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Influence (plain)</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Candidate-theme influence</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>Draw</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>Destroy</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>Draw per destroyed</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>Gain (cost up to)</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>Recover</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>Per kind played</t>
-        </is>
-      </c>
-      <c r="R1" s="4" t="inlineStr">
-        <is>
-          <t>Look at top</t>
-        </is>
-      </c>
-      <c r="S1" s="4" t="inlineStr">
-        <is>
-          <t>Stays in play</t>
-        </is>
-      </c>
-      <c r="T1" s="4" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="U1" s="4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>1796-nation</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>1796</v>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>John Adams</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>The Federalist Administration</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="5" t="n"/>
-      <c r="U2" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence, draw a card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>1796-states</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>1796</v>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>The Republican Societies</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="5" t="n"/>
-      <c r="U3" s="6" t="inlineStr">
-        <is>
-          <t>Draw 2 cards.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>1800-nation</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>John Adams</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>The Alien and Sedition Acts</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>discard</t>
-        </is>
-      </c>
-      <c r="U4" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence. Attack: each rival paper discards a card at random.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>1800-states</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>The Revolution of 1800</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence, draw 2 cards, then you may destroy a card in your hand or discard pile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>1804-nation</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>1804</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>The Louisiana Purchase</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence. Gain a story costing 4 or less from the exchange.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>1804-states</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>1804</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Charles C. Pinckney</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Federalist Commerce</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence, then you may destroy a card in your hand or discard pile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>1808-nation</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>1808</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>James Madison</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>The Embargo</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="6" t="inlineStr">
-        <is>
-          <t>+4 influence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>1808-states</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>1808</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Charles C. Pinckney</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Free Trade and Sailors' Rights</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="6" t="inlineStr">
-        <is>
-          <t>Gain a story costing 5 or less from the exchange.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>1812-nation</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>1812</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>James Madison</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Mr. Madison's War</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="6" t="inlineStr">
-        <is>
-          <t>+1 influence for each different kind of card you play this turn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>1812-states</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>1812</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>DeWitt Clinton</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>The Peace Ticket</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence, draw 2 cards.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>1816-nation</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>1816</v>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>James Monroe</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>The Era of Good Feelings</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="6" t="inlineStr">
-        <is>
-          <t>Draw 3 cards.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>1816-states</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>1816</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Rufus King</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>The Last Federalist</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence. Put a card from your discard pile into your hand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>1820-nation</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>1820</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>John Quincy Adams</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>An Antislavery Diary</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>+1 influence. Look at the top 3 stories of the main deck; put one into your hand, the rest on the bottom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>1820-states</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>1820</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>James Monroe</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>The Missouri Compromise</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>Destroy up to 2 cards in your hand or discard pile; draw a card for each.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>1824-nation</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>1824</v>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>John Quincy Adams</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>The Corrupt Bargain</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>Put up to 2 cards from your discard pile into your hand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>1824-states</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1824</v>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Andrew Jackson</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>The People's Choice</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>+4 influence, draw a card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>1828-nation</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>1828</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>John Quincy Adams</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>The American System</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>Gain a story costing 5 or less from the exchange. Draw a card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>1828-states</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>1828</v>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Andrew Jackson</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Jacksonian Democracy</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence, draw a card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>1832-nation</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>1832</v>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Henry Clay</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>The Bank Recharter</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence. Gain a story costing 4 or less from the exchange.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>1832-states</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>1832</v>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Andrew Jackson</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>The Bank War</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="5" t="n"/>
-      <c r="U21" s="6" t="inlineStr">
-        <is>
-          <t>Gain a story costing 6 or less from the exchange. Draw a card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>1836-nation</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>1836</v>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>William Henry Harrison</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>The Whig Coalition</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="5" t="n"/>
-      <c r="U22" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence, and +1 for each different kind of card you play this turn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>1836-states</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>1836</v>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Martin Van Buren</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>The Specie Circular</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="5" t="n"/>
-      <c r="U23" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence, draw 2 cards.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>1840-nation</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>1840</v>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>William Henry Harrison</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Log Cabin and Hard Cider</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="6" t="inlineStr">
-        <is>
-          <t>+4 influence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>1840-states</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>1840</v>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Martin Van Buren</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>The Independent Treasury</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence. Destroy up to 2 cards in your hand or discard pile; draw a card for each.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>1844-nation</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>1844</v>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Henry Clay</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>The Raleigh Letter</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="5" t="n"/>
-      <c r="U26" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence. Put a card from your discard pile into your hand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>1844-states</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>1844</v>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>James K. Polk</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Manifest Destiny</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="S27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="5" t="n"/>
-      <c r="U27" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence. Look at the top 3 stories of the main deck; put one into your hand, the rest on the bottom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>1848-nation</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>1848</v>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Zachary Taylor</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Social</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>Old Rough and Ready</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>discard</t>
-        </is>
-      </c>
-      <c r="U28" s="6" t="inlineStr">
-        <is>
-          <t>+4 influence. Attack: each rival paper discards a card at random.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>1848-states</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>1848</v>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Lewis Cass</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>Popular Sovereignty</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="5" t="n"/>
-      <c r="U29" s="6" t="inlineStr">
-        <is>
-          <t>+1 influence for each different kind of card you play this turn. Draw a card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>1852-nation</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>1852</v>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Winfield Scott</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Old Fuss and Feathers</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="5" t="n"/>
-      <c r="U30" s="6" t="inlineStr">
-        <is>
-          <t>+5 influence, draw a card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>1852-states</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>1852</v>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Franklin Pierce</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>The Compromise of 1850</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="5" t="n"/>
-      <c r="U31" s="6" t="inlineStr">
-        <is>
-          <t>Destroy up to 3 cards in your hand or discard pile; draw a card for each.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>1856-nation</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>1856</v>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>John C. Fremont</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Free Soil, Free Men, Fremont</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="5" t="n"/>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence, draw 2 cards, then you may destroy a card in your hand or discard pile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>1856-states</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>1856</v>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>James Buchanan</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>Bleeding Kansas</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>scandal</t>
-        </is>
-      </c>
-      <c r="U33" s="6" t="inlineStr">
-        <is>
-          <t>+5 influence. Attack: each rival paper gains a Scandal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>1860-nation</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>1860</v>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>nation</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Abraham Lincoln</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Political</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>A House Divided</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="5" t="n"/>
-      <c r="U34" s="6" t="inlineStr">
-        <is>
-          <t>The last election: the game ends after this turn. Worth 1 prestige for each election card you hold, this one included.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>1860-states</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>1860</v>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>states</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Stephen A. Douglas</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>The Little Giant</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="5" t="n"/>
-      <c r="U35" s="6" t="inlineStr">
-        <is>
-          <t>The last election: the game ends after this turn. Worth 2 prestige, plus 1 for each election card you hold, this one included.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:U35"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15667,7 +15531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15698,22 +15562,22 @@
       <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Card type</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Kinds</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Copies</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Total prestige (vp x copies)</t>
         </is>
@@ -16013,11 +15877,11 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Candidates: fixed prestige on all 34 cards (1860 is also worth 1 per office held)</t>
+          <t>Elections: fixed prestige on all 34 cards (1860 is also worth 1 per office held)</t>
         </is>
       </c>
       <c r="B19" s="2">
-        <f>SUM(Candidates!$H$2:$H$35)</f>
+        <f>SUM(Elections!$J$2:$J$35)</f>
         <v/>
       </c>
       <c r="C19" s="2" t="n"/>

--- a/docs/fourth-estate-cards.xlsx
+++ b/docs/fourth-estate-cards.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stories'!$A$1:$AC$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Elections'!$A$1:$AA$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Elections'!$A$1:$U$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Newspapers'!$A$1:$F$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,28 +642,28 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>the power when played: Influence (plain); Candidate-theme influence (his theme); Draw; Destroy (up to N cards from hand or discard);</t>
+          <t>when played: Influence (plain) = plain influence; Candidate-theme influence = influence of his theme;</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Draw per destroyed (1 = draw a card for each); Gain (cost up to) a story from the exchange; Recover (cards from discard to hand);</t>
+          <t>Action 1 = the draw (Draw N cards; blank if none); Action 2 and Action 3 = its other actions: Destroy up to N cards (draw 1 for each),</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Per kind played (+N per different kind of card played this turn); Look at top (look at the top N of the main deck, keep 1);</t>
+          <t>Gain a story costing N or less, Recover N cards from discard, +N influence per kind of card played, Look at the top N (keep 1),</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Stays in play (+N each turn; none now); Attack (discard or scandal, every rival); Power = the card's text.</t>
+          <t>Attack (each rival discards a card / gains a Scandal); Power = the card's full text.</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11639,20 +11639,14 @@
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="9" customWidth="1" min="22" max="22"/>
-    <col width="55" customWidth="1" min="23" max="23"/>
-    <col width="24" customWidth="1" min="24" max="24"/>
-    <col width="45" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="55" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="45" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -11723,70 +11717,40 @@
       </c>
       <c r="N1" s="4" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Action 1</t>
         </is>
       </c>
       <c r="O1" s="4" t="inlineStr">
         <is>
-          <t>Destroy</t>
+          <t>Action 2</t>
         </is>
       </c>
       <c r="P1" s="4" t="inlineStr">
         <is>
-          <t>Draw per destroyed</t>
+          <t>Action 3</t>
         </is>
       </c>
       <c r="Q1" s="4" t="inlineStr">
         <is>
-          <t>Gain (cost up to)</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="R1" s="4" t="inlineStr">
         <is>
-          <t>Recover</t>
+          <t>fa_name</t>
         </is>
       </c>
       <c r="S1" s="4" t="inlineStr">
         <is>
-          <t>Per kind played</t>
+          <t>First Appearance</t>
         </is>
       </c>
       <c r="T1" s="4" t="inlineStr">
         <is>
-          <t>Look at top</t>
+          <t>fa_kind</t>
         </is>
       </c>
       <c r="U1" s="4" t="inlineStr">
-        <is>
-          <t>Stays in play</t>
-        </is>
-      </c>
-      <c r="V1" s="4" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="W1" s="4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="X1" s="4" t="inlineStr">
-        <is>
-          <t>fa_name</t>
-        </is>
-      </c>
-      <c r="Y1" s="4" t="inlineStr">
-        <is>
-          <t>First Appearance</t>
-        </is>
-      </c>
-      <c r="Z1" s="4" t="inlineStr">
-        <is>
-          <t>fa_kind</t>
-        </is>
-      </c>
-      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>First Appearance: how many</t>
         </is>
@@ -11846,40 +11810,22 @@
       <c r="M2" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="N2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="6" t="n"/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence, draw a card.</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="n"/>
+      <c r="S2" s="6" t="n"/>
+      <c r="T2" s="5" t="n"/>
       <c r="U2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="5" t="n"/>
-      <c r="W2" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence, draw a card.</t>
-        </is>
-      </c>
-      <c r="X2" s="6" t="n"/>
-      <c r="Y2" s="6" t="n"/>
-      <c r="Z2" s="5" t="n"/>
-      <c r="AA2" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11933,40 +11879,22 @@
       <c r="M3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="N3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>Draw 2 cards</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="6" t="n"/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>Draw 2 cards.</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="n"/>
+      <c r="S3" s="6" t="n"/>
+      <c r="T3" s="5" t="n"/>
       <c r="U3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="5" t="n"/>
-      <c r="W3" s="6" t="inlineStr">
-        <is>
-          <t>Draw 2 cards.</t>
-        </is>
-      </c>
-      <c r="X3" s="6" t="n"/>
-      <c r="Y3" s="6" t="n"/>
-      <c r="Z3" s="5" t="n"/>
-      <c r="AA3" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12020,56 +11948,34 @@
       <c r="M4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="7" t="n">
-        <v>0</v>
+      <c r="N4" s="8" t="n"/>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>Attack: each rival discards a card</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="n"/>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>+2 influence. Attack: each rival paper discards a card at random.</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
+        <is>
+          <t>The Sedition Act</t>
+        </is>
+      </c>
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards a card at random.</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
       </c>
       <c r="U4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="7" t="inlineStr">
-        <is>
-          <t>discard</t>
-        </is>
-      </c>
-      <c r="W4" s="8" t="inlineStr">
-        <is>
-          <t>+2 influence. Attack: each rival paper discards a card at random.</t>
-        </is>
-      </c>
-      <c r="X4" s="8" t="inlineStr">
-        <is>
-          <t>The Sedition Act</t>
-        </is>
-      </c>
-      <c r="Y4" s="8" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards a card at random.</t>
-        </is>
-      </c>
-      <c r="Z4" s="7" t="inlineStr">
-        <is>
-          <t>discard_leader</t>
-        </is>
-      </c>
-      <c r="AA4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12127,52 +12033,38 @@
       <c r="M5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="N5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="7" t="n">
-        <v>0</v>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>Draw 2 cards</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>Destroy up to 1 card</t>
+        </is>
+      </c>
+      <c r="P5" s="8" t="n"/>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>+2 influence, draw 2 cards, then you may destroy a card in your hand or discard pile.</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>The Sedition Act</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards a card at random.</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
       </c>
       <c r="U5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="8" t="inlineStr">
-        <is>
-          <t>+2 influence, draw 2 cards, then you may destroy a card in your hand or discard pile.</t>
-        </is>
-      </c>
-      <c r="X5" s="8" t="inlineStr">
-        <is>
-          <t>The Sedition Act</t>
-        </is>
-      </c>
-      <c r="Y5" s="8" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards a card at random.</t>
-        </is>
-      </c>
-      <c r="Z5" s="7" t="inlineStr">
-        <is>
-          <t>discard_leader</t>
-        </is>
-      </c>
-      <c r="AA5" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12230,52 +12122,34 @@
       <c r="M6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>0</v>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>Gain a story costing 4 or less</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence. Gain a story costing 4 or less from the exchange.</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>The Twelfth Amendment</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>Each paper draws a card.</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
       </c>
       <c r="U6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence. Gain a story costing 4 or less from the exchange.</t>
-        </is>
-      </c>
-      <c r="X6" s="6" t="inlineStr">
-        <is>
-          <t>The Twelfth Amendment</t>
-        </is>
-      </c>
-      <c r="Y6" s="6" t="inlineStr">
-        <is>
-          <t>Each paper draws a card.</t>
-        </is>
-      </c>
-      <c r="Z6" s="5" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="AA6" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12329,52 +12203,34 @@
       <c r="M7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="5" t="n">
-        <v>0</v>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>Destroy up to 1 card</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence, then you may destroy a card in your hand or discard pile.</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>The Twelfth Amendment</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Each paper draws a card.</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
       </c>
       <c r="U7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence, then you may destroy a card in your hand or discard pile.</t>
-        </is>
-      </c>
-      <c r="X7" s="6" t="inlineStr">
-        <is>
-          <t>The Twelfth Amendment</t>
-        </is>
-      </c>
-      <c r="Y7" s="6" t="inlineStr">
-        <is>
-          <t>Each paper draws a card.</t>
-        </is>
-      </c>
-      <c r="Z7" s="5" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="AA7" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12432,52 +12288,30 @@
       <c r="M8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="N8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="7" t="n">
-        <v>0</v>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>+4 influence.</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>The Embargo</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>Each paper discards the most expensive card in its hand.</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>discard_dearest</t>
+        </is>
       </c>
       <c r="U8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t>+4 influence.</t>
-        </is>
-      </c>
-      <c r="X8" s="8" t="inlineStr">
-        <is>
-          <t>The Embargo</t>
-        </is>
-      </c>
-      <c r="Y8" s="8" t="inlineStr">
-        <is>
-          <t>Each paper discards the most expensive card in its hand.</t>
-        </is>
-      </c>
-      <c r="Z8" s="7" t="inlineStr">
-        <is>
-          <t>discard_dearest</t>
-        </is>
-      </c>
-      <c r="AA8" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12531,52 +12365,34 @@
       <c r="M9" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="N9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="7" t="n">
-        <v>0</v>
+      <c r="N9" s="8" t="n"/>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>Gain a story costing 5 or less</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>Gain a story costing 5 or less from the exchange.</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>The Embargo</t>
+        </is>
+      </c>
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>Each paper discards the most expensive card in its hand.</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>discard_dearest</t>
+        </is>
       </c>
       <c r="U9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="7" t="n"/>
-      <c r="W9" s="8" t="inlineStr">
-        <is>
-          <t>Gain a story costing 5 or less from the exchange.</t>
-        </is>
-      </c>
-      <c r="X9" s="8" t="inlineStr">
-        <is>
-          <t>The Embargo</t>
-        </is>
-      </c>
-      <c r="Y9" s="8" t="inlineStr">
-        <is>
-          <t>Each paper discards the most expensive card in its hand.</t>
-        </is>
-      </c>
-      <c r="Z9" s="7" t="inlineStr">
-        <is>
-          <t>discard_dearest</t>
-        </is>
-      </c>
-      <c r="AA9" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12634,52 +12450,34 @@
       <c r="M10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="N10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>0</v>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>+1 influence per kind of card played</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="n"/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>+1 influence for each different kind of card you play this turn.</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Impressment</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
       </c>
       <c r="U10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="6" t="inlineStr">
-        <is>
-          <t>+1 influence for each different kind of card you play this turn.</t>
-        </is>
-      </c>
-      <c r="X10" s="6" t="inlineStr">
-        <is>
-          <t>Impressment</t>
-        </is>
-      </c>
-      <c r="Y10" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="Z10" s="5" t="inlineStr">
-        <is>
-          <t>scandal_leader</t>
-        </is>
-      </c>
-      <c r="AA10" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12733,52 +12531,34 @@
       <c r="M11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="N11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="5" t="n">
-        <v>0</v>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>Draw 2 cards</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence, draw 2 cards.</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Impressment</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
       </c>
       <c r="U11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence, draw 2 cards.</t>
-        </is>
-      </c>
-      <c r="X11" s="6" t="inlineStr">
-        <is>
-          <t>Impressment</t>
-        </is>
-      </c>
-      <c r="Y11" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="Z11" s="5" t="inlineStr">
-        <is>
-          <t>scandal_leader</t>
-        </is>
-      </c>
-      <c r="AA11" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12836,52 +12616,34 @@
       <c r="M12" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="N12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="7" t="n">
-        <v>0</v>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>Draw 3 cards</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="n"/>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>Draw 3 cards.</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>Good Feelings</t>
+        </is>
+      </c>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t>Each paper destroys a Scandal in its hand or discard pile.</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>unscandal</t>
+        </is>
       </c>
       <c r="U12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="7" t="n"/>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>Draw 3 cards.</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>Good Feelings</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>Each paper destroys a Scandal in its hand or discard pile.</t>
-        </is>
-      </c>
-      <c r="Z12" s="7" t="inlineStr">
-        <is>
-          <t>unscandal</t>
-        </is>
-      </c>
-      <c r="AA12" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12935,52 +12697,34 @@
       <c r="M13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="N13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="7" t="n">
-        <v>0</v>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>Recover 1 card from discard</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>+2 influence. Put a card from your discard pile into your hand.</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>Good Feelings</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>Each paper destroys a Scandal in its hand or discard pile.</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>unscandal</t>
+        </is>
       </c>
       <c r="U13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="7" t="n"/>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>+2 influence. Put a card from your discard pile into your hand.</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>Good Feelings</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>Each paper destroys a Scandal in its hand or discard pile.</t>
-        </is>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
-        <is>
-          <t>unscandal</t>
-        </is>
-      </c>
-      <c r="AA13" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13034,52 +12778,34 @@
       <c r="M14" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>3</v>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>Look at the top 3, keep 1</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>+1 influence. Look at the top 3 stories of the main deck; put one into your hand, the rest on the bottom.</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>A Fire Bell in the Night</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards a card at random.</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
       </c>
       <c r="U14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="6" t="inlineStr">
-        <is>
-          <t>+1 influence. Look at the top 3 stories of the main deck; put one into your hand, the rest on the bottom.</t>
-        </is>
-      </c>
-      <c r="X14" s="6" t="inlineStr">
-        <is>
-          <t>A Fire Bell in the Night</t>
-        </is>
-      </c>
-      <c r="Y14" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards a card at random.</t>
-        </is>
-      </c>
-      <c r="Z14" s="5" t="inlineStr">
-        <is>
-          <t>discard_leader</t>
-        </is>
-      </c>
-      <c r="AA14" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13137,52 +12863,34 @@
       <c r="M15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="5" t="n">
-        <v>0</v>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>Destroy up to 2 cards, draw 1 for each</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Destroy up to 2 cards in your hand or discard pile; draw a card for each.</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>A Fire Bell in the Night</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards a card at random.</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
       </c>
       <c r="U15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="6" t="inlineStr">
-        <is>
-          <t>Destroy up to 2 cards in your hand or discard pile; draw a card for each.</t>
-        </is>
-      </c>
-      <c r="X15" s="6" t="inlineStr">
-        <is>
-          <t>A Fire Bell in the Night</t>
-        </is>
-      </c>
-      <c r="Y15" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards a card at random.</t>
-        </is>
-      </c>
-      <c r="Z15" s="5" t="inlineStr">
-        <is>
-          <t>discard_leader</t>
-        </is>
-      </c>
-      <c r="AA15" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13240,52 +12948,34 @@
       <c r="M16" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="N16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="7" t="n">
-        <v>0</v>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>Recover 2 cards from discard</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>Put up to 2 cards from your discard pile into your hand.</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>The Corrupt Bargain</t>
+        </is>
+      </c>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
       </c>
       <c r="U16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="7" t="n"/>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>Put up to 2 cards from your discard pile into your hand.</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>The Corrupt Bargain</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
-        <is>
-          <t>scandal_leader</t>
-        </is>
-      </c>
-      <c r="AA16" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13339,52 +13029,34 @@
       <c r="M17" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="N17" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="7" t="n">
-        <v>0</v>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>Draw 1 card</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>+4 influence, draw a card.</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>The Corrupt Bargain</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
       </c>
       <c r="U17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="7" t="n"/>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>+4 influence, draw a card.</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t>The Corrupt Bargain</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
-        <is>
-          <t>scandal_leader</t>
-        </is>
-      </c>
-      <c r="AA17" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13438,52 +13110,38 @@
       <c r="M18" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="5" t="n">
-        <v>0</v>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>Gain a story costing 5 or less</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Gain a story costing 5 or less from the exchange. Draw a card.</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Mudslinging</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
       </c>
       <c r="U18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="5" t="n"/>
-      <c r="W18" s="6" t="inlineStr">
-        <is>
-          <t>Gain a story costing 5 or less from the exchange. Draw a card.</t>
-        </is>
-      </c>
-      <c r="X18" s="6" t="inlineStr">
-        <is>
-          <t>Mudslinging</t>
-        </is>
-      </c>
-      <c r="Y18" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="Z18" s="5" t="inlineStr">
-        <is>
-          <t>scandal_leader</t>
-        </is>
-      </c>
-      <c r="AA18" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13541,52 +13199,34 @@
       <c r="M19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="5" t="n">
-        <v>0</v>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence, draw a card.</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Mudslinging</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
       </c>
       <c r="U19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="5" t="n"/>
-      <c r="W19" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence, draw a card.</t>
-        </is>
-      </c>
-      <c r="X19" s="6" t="inlineStr">
-        <is>
-          <t>Mudslinging</t>
-        </is>
-      </c>
-      <c r="Y19" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="Z19" s="5" t="inlineStr">
-        <is>
-          <t>scandal_leader</t>
-        </is>
-      </c>
-      <c r="AA19" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13640,52 +13280,34 @@
       <c r="M20" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="N20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="7" t="n">
-        <v>0</v>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>Gain a story costing 4 or less</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>+3 influence. Gain a story costing 4 or less from the exchange.</t>
+        </is>
+      </c>
+      <c r="R20" s="8" t="inlineStr">
+        <is>
+          <t>The Veto</t>
+        </is>
+      </c>
+      <c r="S20" s="8" t="inlineStr">
+        <is>
+          <t>The exchange is swept and dealt afresh.</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr">
+        <is>
+          <t>sweep</t>
+        </is>
       </c>
       <c r="U20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="7" t="n"/>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>+3 influence. Gain a story costing 4 or less from the exchange.</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t>The Veto</t>
-        </is>
-      </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>The exchange is swept and dealt afresh.</t>
-        </is>
-      </c>
-      <c r="Z20" s="7" t="inlineStr">
-        <is>
-          <t>sweep</t>
-        </is>
-      </c>
-      <c r="AA20" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13743,52 +13365,38 @@
       <c r="M21" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="N21" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="7" t="n">
-        <v>0</v>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>Draw 1 card</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>Gain a story costing 6 or less</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="n"/>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>Gain a story costing 6 or less from the exchange. Draw a card.</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>The Veto</t>
+        </is>
+      </c>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>The exchange is swept and dealt afresh.</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>sweep</t>
+        </is>
       </c>
       <c r="U21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="7" t="n"/>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>Gain a story costing 6 or less from the exchange. Draw a card.</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t>The Veto</t>
-        </is>
-      </c>
-      <c r="Y21" s="8" t="inlineStr">
-        <is>
-          <t>The exchange is swept and dealt afresh.</t>
-        </is>
-      </c>
-      <c r="Z21" s="7" t="inlineStr">
-        <is>
-          <t>sweep</t>
-        </is>
-      </c>
-      <c r="AA21" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13842,52 +13450,34 @@
       <c r="M22" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" s="5" t="n">
-        <v>0</v>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>+1 influence per kind of card played</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence, and +1 for each different kind of card you play this turn.</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>The Panic of 1837</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
       </c>
       <c r="U22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence, and +1 for each different kind of card you play this turn.</t>
-        </is>
-      </c>
-      <c r="X22" s="6" t="inlineStr">
-        <is>
-          <t>The Panic of 1837</t>
-        </is>
-      </c>
-      <c r="Y22" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
-        </is>
-      </c>
-      <c r="Z22" s="5" t="inlineStr">
-        <is>
-          <t>discard_leader</t>
-        </is>
-      </c>
-      <c r="AA22" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13945,52 +13535,34 @@
       <c r="M23" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="N23" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="5" t="n">
-        <v>0</v>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>Draw 2 cards</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence, draw 2 cards.</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>The Panic of 1837</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
       </c>
       <c r="U23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="5" t="n"/>
-      <c r="W23" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence, draw 2 cards.</t>
-        </is>
-      </c>
-      <c r="X23" s="6" t="inlineStr">
-        <is>
-          <t>The Panic of 1837</t>
-        </is>
-      </c>
-      <c r="Y23" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
-        </is>
-      </c>
-      <c r="Z23" s="5" t="inlineStr">
-        <is>
-          <t>discard_leader</t>
-        </is>
-      </c>
-      <c r="AA23" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14048,52 +13620,30 @@
       <c r="M24" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="N24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="7" t="n">
-        <v>0</v>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
+      <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>+4 influence.</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
+          <t>Tippecanoe and Tyler Too</t>
+        </is>
+      </c>
+      <c r="S24" s="8" t="inlineStr">
+        <is>
+          <t>Each paper draws a card.</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
       </c>
       <c r="U24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="7" t="n"/>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t>+4 influence.</t>
-        </is>
-      </c>
-      <c r="X24" s="8" t="inlineStr">
-        <is>
-          <t>Tippecanoe and Tyler Too</t>
-        </is>
-      </c>
-      <c r="Y24" s="8" t="inlineStr">
-        <is>
-          <t>Each paper draws a card.</t>
-        </is>
-      </c>
-      <c r="Z24" s="7" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="AA24" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14147,52 +13697,34 @@
       <c r="M25" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="N25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="P25" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="7" t="n">
-        <v>0</v>
+      <c r="N25" s="8" t="n"/>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>Destroy up to 2 cards, draw 1 for each</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="n"/>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>+2 influence. Destroy up to 2 cards in your hand or discard pile; draw a card for each.</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>Tippecanoe and Tyler Too</t>
+        </is>
+      </c>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t>Each paper draws a card.</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
       </c>
       <c r="U25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="7" t="n"/>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>+2 influence. Destroy up to 2 cards in your hand or discard pile; draw a card for each.</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t>Tippecanoe and Tyler Too</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>Each paper draws a card.</t>
-        </is>
-      </c>
-      <c r="Z25" s="7" t="inlineStr">
-        <is>
-          <t>draw</t>
-        </is>
-      </c>
-      <c r="AA25" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14246,52 +13778,34 @@
       <c r="M26" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="5" t="n">
-        <v>0</v>
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>Recover 1 card from discard</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="n"/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>+3 influence. Put a card from your discard pile into your hand.</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Fifty-four Forty</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the fewest offices draws 2 cards.</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="inlineStr">
+        <is>
+          <t>draw_fewest</t>
+        </is>
       </c>
       <c r="U26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="5" t="n"/>
-      <c r="W26" s="6" t="inlineStr">
-        <is>
-          <t>+3 influence. Put a card from your discard pile into your hand.</t>
-        </is>
-      </c>
-      <c r="X26" s="6" t="inlineStr">
-        <is>
-          <t>Fifty-four Forty</t>
-        </is>
-      </c>
-      <c r="Y26" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the fewest offices draws 2 cards.</t>
-        </is>
-      </c>
-      <c r="Z26" s="5" t="inlineStr">
-        <is>
-          <t>draw_fewest</t>
-        </is>
-      </c>
-      <c r="AA26" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14349,52 +13863,34 @@
       <c r="M27" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="N27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="5" t="n">
-        <v>3</v>
+      <c r="N27" s="6" t="n"/>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>Look at the top 3, keep 1</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="n"/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>+2 influence. Look at the top 3 stories of the main deck; put one into your hand, the rest on the bottom.</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Fifty-four Forty</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the fewest offices draws 2 cards.</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>draw_fewest</t>
+        </is>
       </c>
       <c r="U27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="5" t="n"/>
-      <c r="W27" s="6" t="inlineStr">
-        <is>
-          <t>+2 influence. Look at the top 3 stories of the main deck; put one into your hand, the rest on the bottom.</t>
-        </is>
-      </c>
-      <c r="X27" s="6" t="inlineStr">
-        <is>
-          <t>Fifty-four Forty</t>
-        </is>
-      </c>
-      <c r="Y27" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the fewest offices draws 2 cards.</t>
-        </is>
-      </c>
-      <c r="Z27" s="5" t="inlineStr">
-        <is>
-          <t>draw_fewest</t>
-        </is>
-      </c>
-      <c r="AA27" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14452,56 +13948,34 @@
       <c r="M28" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="N28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="7" t="n">
-        <v>0</v>
+      <c r="N28" s="8" t="n"/>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>Attack: each rival discards a card</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="n"/>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>+4 influence. Attack: each rival paper discards a card at random.</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>The Wilmot Proviso</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>Each paper destroys the cheapest card in its hand.</t>
+        </is>
+      </c>
+      <c r="T28" s="7" t="inlineStr">
+        <is>
+          <t>destroy_cheapest</t>
+        </is>
       </c>
       <c r="U28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="7" t="inlineStr">
-        <is>
-          <t>discard</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t>+4 influence. Attack: each rival paper discards a card at random.</t>
-        </is>
-      </c>
-      <c r="X28" s="8" t="inlineStr">
-        <is>
-          <t>The Wilmot Proviso</t>
-        </is>
-      </c>
-      <c r="Y28" s="8" t="inlineStr">
-        <is>
-          <t>Each paper destroys the cheapest card in its hand.</t>
-        </is>
-      </c>
-      <c r="Z28" s="7" t="inlineStr">
-        <is>
-          <t>destroy_cheapest</t>
-        </is>
-      </c>
-      <c r="AA28" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14555,52 +14029,38 @@
       <c r="M29" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="N29" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" s="7" t="n">
-        <v>0</v>
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t>Draw 1 card</t>
+        </is>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>+1 influence per kind of card played</t>
+        </is>
+      </c>
+      <c r="P29" s="8" t="n"/>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>+1 influence for each different kind of card you play this turn. Draw a card.</t>
+        </is>
+      </c>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>The Wilmot Proviso</t>
+        </is>
+      </c>
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t>Each paper destroys the cheapest card in its hand.</t>
+        </is>
+      </c>
+      <c r="T29" s="7" t="inlineStr">
+        <is>
+          <t>destroy_cheapest</t>
+        </is>
       </c>
       <c r="U29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="7" t="n"/>
-      <c r="W29" s="8" t="inlineStr">
-        <is>
-          <t>+1 influence for each different kind of card you play this turn. Draw a card.</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t>The Wilmot Proviso</t>
-        </is>
-      </c>
-      <c r="Y29" s="8" t="inlineStr">
-        <is>
-          <t>Each paper destroys the cheapest card in its hand.</t>
-        </is>
-      </c>
-      <c r="Z29" s="7" t="inlineStr">
-        <is>
-          <t>destroy_cheapest</t>
-        </is>
-      </c>
-      <c r="AA29" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14654,52 +14114,34 @@
       <c r="M30" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="N30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="5" t="n">
-        <v>0</v>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>Draw 1 card</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="n"/>
+      <c r="P30" s="6" t="n"/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>+5 influence, draw a card.</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>The Fugitive Slave Act</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
       </c>
       <c r="U30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="5" t="n"/>
-      <c r="W30" s="6" t="inlineStr">
-        <is>
-          <t>+5 influence, draw a card.</t>
-        </is>
-      </c>
-      <c r="X30" s="6" t="inlineStr">
-        <is>
-          <t>The Fugitive Slave Act</t>
-        </is>
-      </c>
-      <c r="Y30" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="Z30" s="5" t="inlineStr">
-        <is>
-          <t>scandal_leader</t>
-        </is>
-      </c>
-      <c r="AA30" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14757,52 +14199,34 @@
       <c r="M31" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="N31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="5" t="n">
-        <v>0</v>
+      <c r="N31" s="6" t="n"/>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>Destroy up to 3 cards, draw 1 for each</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="n"/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Destroy up to 3 cards in your hand or discard pile; draw a card for each.</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>The Fugitive Slave Act</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="inlineStr">
+        <is>
+          <t>scandal_leader</t>
+        </is>
       </c>
       <c r="U31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="5" t="n"/>
-      <c r="W31" s="6" t="inlineStr">
-        <is>
-          <t>Destroy up to 3 cards in your hand or discard pile; draw a card for each.</t>
-        </is>
-      </c>
-      <c r="X31" s="6" t="inlineStr">
-        <is>
-          <t>The Fugitive Slave Act</t>
-        </is>
-      </c>
-      <c r="Y31" s="6" t="inlineStr">
-        <is>
-          <t>The paper (or papers) with the most prestige gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="Z31" s="5" t="inlineStr">
-        <is>
-          <t>scandal_leader</t>
-        </is>
-      </c>
-      <c r="AA31" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14856,52 +14280,38 @@
       <c r="M32" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="N32" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="7" t="n">
-        <v>0</v>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>Draw 2 cards</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>Destroy up to 1 card</t>
+        </is>
+      </c>
+      <c r="P32" s="8" t="n"/>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>+3 influence, draw 2 cards, then you may destroy a card in your hand or discard pile.</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>Bleeding Kansas</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
+        </is>
+      </c>
+      <c r="T32" s="7" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
       </c>
       <c r="U32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="7" t="n"/>
-      <c r="W32" s="8" t="inlineStr">
-        <is>
-          <t>+3 influence, draw 2 cards, then you may destroy a card in your hand or discard pile.</t>
-        </is>
-      </c>
-      <c r="X32" s="8" t="inlineStr">
-        <is>
-          <t>Bleeding Kansas</t>
-        </is>
-      </c>
-      <c r="Y32" s="8" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
-        </is>
-      </c>
-      <c r="Z32" s="7" t="inlineStr">
-        <is>
-          <t>discard_leader</t>
-        </is>
-      </c>
-      <c r="AA32" s="7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14959,56 +14369,34 @@
       <c r="M33" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="N33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="7" t="n">
-        <v>0</v>
+      <c r="N33" s="8" t="n"/>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>Attack: each rival gains a Scandal</t>
+        </is>
+      </c>
+      <c r="P33" s="8" t="n"/>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t>+5 influence. Attack: each rival paper gains a Scandal.</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t>Bleeding Kansas</t>
+        </is>
+      </c>
+      <c r="S33" s="8" t="inlineStr">
+        <is>
+          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
+        </is>
+      </c>
+      <c r="T33" s="7" t="inlineStr">
+        <is>
+          <t>discard_leader</t>
+        </is>
       </c>
       <c r="U33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="7" t="inlineStr">
-        <is>
-          <t>scandal</t>
-        </is>
-      </c>
-      <c r="W33" s="8" t="inlineStr">
-        <is>
-          <t>+5 influence. Attack: each rival paper gains a Scandal.</t>
-        </is>
-      </c>
-      <c r="X33" s="8" t="inlineStr">
-        <is>
-          <t>Bleeding Kansas</t>
-        </is>
-      </c>
-      <c r="Y33" s="8" t="inlineStr">
-        <is>
-          <t>The paper (or papers) holding the most offices discards 2 cards at random.</t>
-        </is>
-      </c>
-      <c r="Z33" s="7" t="inlineStr">
-        <is>
-          <t>discard_leader</t>
-        </is>
-      </c>
-      <c r="AA33" s="7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -15066,52 +14454,30 @@
       <c r="M34" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="N34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="5" t="n">
-        <v>0</v>
+      <c r="N34" s="6" t="n"/>
+      <c r="O34" s="6" t="n"/>
+      <c r="P34" s="6" t="n"/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>The last election: the game ends after this turn. Worth 1 prestige for each election card you hold, this one included.</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Secession</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Each paper destroys the cheapest card in its hand.</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <t>destroy_cheapest</t>
+        </is>
       </c>
       <c r="U34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="5" t="n"/>
-      <c r="W34" s="6" t="inlineStr">
-        <is>
-          <t>The last election: the game ends after this turn. Worth 1 prestige for each election card you hold, this one included.</t>
-        </is>
-      </c>
-      <c r="X34" s="6" t="inlineStr">
-        <is>
-          <t>Secession</t>
-        </is>
-      </c>
-      <c r="Y34" s="6" t="inlineStr">
-        <is>
-          <t>Each paper destroys the cheapest card in its hand.</t>
-        </is>
-      </c>
-      <c r="Z34" s="5" t="inlineStr">
-        <is>
-          <t>destroy_cheapest</t>
-        </is>
-      </c>
-      <c r="AA34" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15165,57 +14531,35 @@
       <c r="M35" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="5" t="n">
-        <v>0</v>
+      <c r="N35" s="6" t="n"/>
+      <c r="O35" s="6" t="n"/>
+      <c r="P35" s="6" t="n"/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>The last election: the game ends after this turn. Worth 2 prestige, plus 1 for each election card you hold, this one included.</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Secession</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Each paper destroys the cheapest card in its hand.</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="inlineStr">
+        <is>
+          <t>destroy_cheapest</t>
+        </is>
       </c>
       <c r="U35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="5" t="n"/>
-      <c r="W35" s="6" t="inlineStr">
-        <is>
-          <t>The last election: the game ends after this turn. Worth 2 prestige, plus 1 for each election card you hold, this one included.</t>
-        </is>
-      </c>
-      <c r="X35" s="6" t="inlineStr">
-        <is>
-          <t>Secession</t>
-        </is>
-      </c>
-      <c r="Y35" s="6" t="inlineStr">
-        <is>
-          <t>Each paper destroys the cheapest card in its hand.</t>
-        </is>
-      </c>
-      <c r="Z35" s="5" t="inlineStr">
-        <is>
-          <t>destroy_cheapest</t>
-        </is>
-      </c>
-      <c r="AA35" s="5" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA35"/>
+  <autoFilter ref="A1:U35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/fourth-estate-cards.xlsx
+++ b/docs/fourth-estate-cards.xlsx
@@ -11,12 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stories" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elections" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newspapers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Art prompts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Stories'!$A$1:$AC$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Elections'!$A$1:$U$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Newspapers'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Art prompts'!$A$1:$H$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -545,137 +547,151 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>Art prompts -- one image-generation prompt per card (144): woodcut to 1819, wood engraving 1820-1835, lithograph 1836-1860.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             Save each image as frontend/public/art/&lt;file&gt;; the card shows it when it is there. Edit the subject in tools/build_art_prompts.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Summary -- counts by type, theme and era, as formulas over the Stories sheet.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Stories columns</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>cost = price on the exchange; Prestige = the score; Influence (plain) = spends on anything;</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Political / Economic / Social influence = influence of that theme (a story has at most one); Campaign influence = elections only;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>draw = cards drawn; trash = cards you may destroy; gain_upto = gain a story costing that or less;</t>
+          <t>cost = price on the exchange; Prestige = the score; Influence (plain) = spends on anything;</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>chain = +N if you play another story of the theme; per_same = +N per other story of the theme; per_office = +N per election won;</t>
+          <t>Political / Economic / Social influence = influence of that theme (a story has at most one); Campaign influence = elections only;</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>attack = discard or scandal (hits every rival); defense = 1 if it blocks an attack; retract = Retraction (draw a card, destroy a Scandal);</t>
+          <t>draw = cards drawn; trash = cards you may destroy; gain_upto = gain a story costing that or less;</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ongoing_gen / ongoing_draw = a media event's bonus to its owner each turn; others_bonus / others_theme = its bonus to every other paper;</t>
+          <t>chain = +N if you play another story of the theme; per_same = +N per other story of the theme; per_office = +N per election won;</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>attack = discard or scandal (hits every rival); defense = 1 if it blocks an attack; retract = Retraction (draw a card, destroy a Scandal);</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ongoing_gen / ongoing_draw = a media event's bonus to its owner each turn; others_bonus / others_theme = its bonus to every other paper;</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>released = the election whose campaign releases it into the main deck; year = the event's date; copies = how many exist.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Elections columns</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>key = year-side (nation or states); History's choice = yes on the candidate history elected (2 cheaper to elect);</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>theme = the influence that counts toward him; threshold = influence needed to elect him; card_name = the card his Patron gains;</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Prestige = the card's prestige; Prestige per office = prestige for each election card its holder owns (1860);</t>
+          <t>key = year-side (nation or states); History's choice = yes on the candidate history elected (2 cheaper to elect);</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>when played: Influence (plain) = plain influence; Candidate-theme influence = influence of his theme;</t>
+          <t>theme = the influence that counts toward him; threshold = influence needed to elect him; card_name = the card his Patron gains;</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Action 1 = the draw (Draw N cards; blank if none); Action 2 and Action 3 = its other actions: Destroy up to N cards (draw 1 for each),</t>
+          <t>Prestige = the card's prestige; Prestige per office = prestige for each election card its holder owns (1860);</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Gain a story costing N or less, Recover N cards from discard, +N influence per kind of card played, Look at the top N (keep 1),</t>
+          <t>when played: Influence (plain) = plain influence; Candidate-theme influence = influence of his theme;</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Attack (each rival discards a card / gains a Scandal); Power = the card's full text.</t>
+          <t>Action 1 = the draw (Draw N cards; blank if none); Action 2 and Action 3 = its other actions: Destroy up to N cards (draw 1 for each),</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>First Appearance = what happens to every paper as that year's campaign opens; fa_kind = which event: discard, discard_leader,</t>
+          <t>Gain a story costing N or less, Recover N cards from discard, +N influence per kind of card played, Look at the top N (keep 1),</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Attack (each rival discards a card / gains a Scandal); Power = the card's full text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>First Appearance = what happens to every paper as that year's campaign opens; fa_kind = which event: discard, discard_leader,</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>discard_dearest, destroy_cheapest, draw, draw_fewest, scandal, scandal_leader, unscandal, sweep; First Appearance: how many = its number.</t>
         </is>
@@ -14881,6 +14897,5833 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H145"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="110" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>prompt</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>letter</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Letter to the Editor</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>1796</v>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>a country gentleman in a tricorne hat at a writing desk by candlelight, quill in hand, sealing a letter addressed to the printer</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1796. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a country gentleman in a tricorne hat at a writing desk by candlelight, quill in hand, sealing a letter addressed to the printer. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>letter.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>notice</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Local Notice</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Starter</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1796</v>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>a small-town village green with a church steeple, a stray cow and a notice board where a man tacks up a handbill</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1796. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a small-town village green with a church steeple, a stray cow and a notice board where a man tacks up a handbill. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>notice.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>editorial</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Editorial</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Editorial</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1796</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>an editor in shirtsleeves at a cluttered desk in a print shop, a hand press behind him, writing with fierce concentration</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1796. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: an editor in shirtsleeves at a cluttered desk in a print shop, a hand press behind him, writing with fierce concentration. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>editorial.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>scandal</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Scandal</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Scandal</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1796</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>a crowd of townspeople whispering behind their hands around a freshly posted broadside, one man pointing accusingly</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1796. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a crowd of townspeople whispering behind their hands around a freshly posted broadside, one man pointing accusingly. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>scandal.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>stamp_act</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>The Stamp Act</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1765</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>a crowd burning a heap of stamped paper in a town square at night, a printer holding up a newspaper bordered in black like a tombstone</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1765. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a crowd burning a heap of stamped paper in a town square at night, a printer holding up a newspaper bordered in black like a tombstone. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>stamp_act.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>boston_massacre</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>The Boston Massacre</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1770</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>British redcoats in a line firing into a crowd of colonists on a snowy Boston street, smoke from the muskets, a brick State House behind</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1770. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: British redcoats in a line firing into a crowd of colonists on a snowy Boston street, smoke from the muskets, a brick State House behind. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>boston_massacre.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>tea_party</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>The Boston Tea Party</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1773</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>men disguised in blankets on a merchant ship at night dumping chests of tea into Boston harbor, a crowd watching from the wharf</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1773. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: men disguised in blankets on a merchant ship at night dumping chests of tea into Boston harbor, a crowd watching from the wharf. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>tea_party.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>common_sense</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Common Sense</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1776</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>a colonist reading a small pamphlet aloud to a rapt group in a tavern, a printer stacking more copies on the counter</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1776. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a colonist reading a small pamphlet aloud to a rapt group in a tavern, a printer stacking more copies on the counter. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>common_sense.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>The Declaration of Independence</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1776</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>a man reading a large broadside aloud from courthouse steps to a crowd raising their hats, a flag on a pole</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1776. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a man reading a large broadside aloud from courthouse steps to a crowd raising their hats, a flag on a pole. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>declaration.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>saratoga</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Saratoga</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1777</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>a British general handing over his sword to an American general before ranks of soldiers in a wooded clearing</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1777. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a British general handing over his sword to an American general before ranks of soldiers in a wooded clearing. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>saratoga.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>valley_forge</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Valley Forge</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1777</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>ragged Continental soldiers huddled around a campfire in deep snow beside log huts, a general on horseback watching</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1777. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: ragged Continental soldiers huddled around a campfire in deep snow beside log huts, a general on horseback watching. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>valley_forge.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>articles_confederation</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>The Articles of Confederation</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1781</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>thirteen delegates seated at a long table, each with his own state's flag, no one at the head of the table</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1781. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: thirteen delegates seated at a long table, each with his own state's flag, no one at the head of the table. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>articles_confederation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>newburgh</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>The Newburgh Conspiracy</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1783</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>George Washington putting on his spectacles to read a letter to a hall of officers, the officers moved and silent</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1783. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: George Washington putting on his spectacles to read a letter to a hall of officers, the officers moved and silent. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>newburgh.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>treaty_of_paris</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>The Treaty of Paris</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1783</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>diplomats in powdered wigs signing a treaty at a table in a Paris salon, a map of North America on the wall</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1783. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: diplomats in powdered wigs signing a treaty at a table in a Paris salon, a map of North America on the wall. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>treaty_of_paris.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>pennsylvania_packet</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>The First American Daily</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Media event</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1784</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>a busy Philadelphia street at dawn, a newsboy carrying a bundle of fresh daily papers past shop fronts</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1784. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a busy Philadelphia street at dawn, a newsboy carrying a bundle of fresh daily papers past shop fronts. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>pennsylvania_packet.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>shays_rebellion</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Shays' Rebellion</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1786</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>armed farmers in rough coats blocking the steps of a county courthouse, a judge turned away at the door</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1786. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: armed farmers in rough coats blocking the steps of a county courthouse, a judge turned away at the door. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>shays_rebellion.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>antifederalist_papers</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Brutus and the Federal Farmer</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1787</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>a stern writer in a Roman toga as 'Brutus' at a desk with a quill, a pile of newspapers and a shadow of a great building looming</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1787. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a stern writer in a Roman toga as 'Brutus' at a desk with a quill, a pile of newspapers and a shadow of a great building looming. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>antifederalist_papers.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>constitutional_convention</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>The Constitutional Convention</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1787</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>delegates in Independence Hall with the windows shut, Washington presiding from a high-backed chair carved with a rising sun</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1787. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: delegates in Independence Hall with the windows shut, Washington presiding from a high-backed chair carved with a rising sun. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>constitutional_convention.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>federalist_papers</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>The Federalist</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1787</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>three gentlemen writing at a candlelit table, a stack of New York newspapers and a bust of a Roman orator</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1787. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: three gentlemen writing at a candlelit table, a stack of New York newspapers and a bust of a Roman orator. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>federalist_papers.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>northwest_ordinance</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>The Northwest Ordinance</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1787</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>surveyors with a chain and compass marking square townships in a forest beside the Ohio River, a flatboat on the water</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1787. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: surveyors with a chain and compass marking square townships in a forest beside the Ohio River, a flatboat on the water. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>northwest_ordinance.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>gazette_of_the_us</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>The Gazette of the United States</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1789</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>a printer pulling the bar of a wooden hand press in a New York shop, sheets drying on lines overhead</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1789. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a printer pulling the bar of a wooden hand press in a New York shop, sheets drying on lines overhead. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>gazette_of_the_us.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>judiciary_act</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>The Judiciary Act</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1789</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>robed judges riding circuit on horseback along a muddy country road toward a small courthouse</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1789. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: robed judges riding circuit on horseback along a muddy country road toward a small courthouse. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>judiciary_act.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>The Assumption of State Debts</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1790</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>speculators in fine coats buying up old war certificates from weary veterans at a tavern table</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1790. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: speculators in fine coats buying up old war certificates from weary veterans at a tavern table. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>assumption.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>residence_act</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>The Residence Act</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1790</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>a surveyor's party on a hill overlooking a wide river and empty wooded land where a capital will be built</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1790. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a surveyor's party on a hill overlooking a wide river and empty wooded land where a capital will be built. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>residence_act.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>bank_of_the_us</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>The Bank of the United States</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1791</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>a classical marble bank building with columns on a Philadelphia street, merchants climbing its steps</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1791. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a classical marble bank building with columns on a Philadelphia street, merchants climbing its steps. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>bank_of_the_us.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>bill_of_rights</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>The Bill of Rights</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1791</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>a printing press with a fresh sheet on it, a church, a citizen speaking from a stump and a jury box, arranged as an allegory of liberty</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1791. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a printing press with a fresh sheet on it, a church, a citizen speaking from a stump and a jury box, arranged as an allegory of liberty. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>bill_of_rights.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>national_gazette</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>The National Gazette</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1791</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>a poet-editor at a desk writing sharply, a quill in hand and a French liberty cap on a peg behind him</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1791. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a poet-editor at a desk writing sharply, a quill in hand and a French liberty cap on a peg behind him. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>national_gazette.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>report_manufactures</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>The Report on Manufactures</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1791</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>a water-powered mill on a river with a spinning wheel and a plough in the foreground, as an allegory of industry</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1791. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a water-powered mill on a river with a spinning wheel and a plough in the foreground, as an allegory of industry. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>report_manufactures.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>rights_of_man</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>The Rights of Man</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1791</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>a crowd in a city square raising a liberty pole topped with a liberty cap, a man reading from a book</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1791. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a crowd in a city square raising a liberty pole topped with a liberty cap, a man reading from a book. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>rights_of_man.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>postal_act_1792</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>The Postal Act of 1792</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Media event</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1792</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>a post rider galloping along a forest road with saddlebags stuffed with newspapers, a post horn at his lips</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1792. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a post rider galloping along a forest road with saddlebags stuffed with newspapers, a post horn at his lips. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>postal_act_1792.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>citizen_genet</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Citizen Genet</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>1793</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>a flamboyant French diplomat in a sash addressing a cheering crowd from a balcony, a cockade on his hat</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1793. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a flamboyant French diplomat in a sash addressing a cheering crowd from a balcony, a cockade on his hat. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>citizen_genet.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>democratic_societies</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>The Democratic-Republican Societies</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1794</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>mechanics and farmers raising glasses at a long tavern table under a French tricolour and an American flag</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1794. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: mechanics and farmers raising glasses at a long tavern table under a French tricolour and an American flag. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>democratic_societies.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>whiskey_rebellion</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>The Whiskey Rebellion</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>1794</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>a column of militia marching over the Allegheny mountains, a farmer's still smoking in a log shed by the road</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1794. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a column of militia marching over the Allegheny mountains, a farmer's still smoking in a log shed by the road. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>whiskey_rebellion.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>jay_treaty</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>The Jay Treaty</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1795</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>a crowd burning a straw effigy in a coat and wig on a pole at night, torches raised</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1795. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a crowd burning a straw effigy in a coat and wig on a pole at night, torches raised. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>jay_treaty.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>alien_sedition</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>The Alien and Sedition Acts</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1798</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>a printer being led from his shop in handcuffs by a marshal, his press and type cases behind</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1798. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a printer being led from his shop in handcuffs by a marshal, his press and type cases behind. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>alien_sedition.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>kentucky_resolutions</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>The Kentucky and Virginia Resolutions</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1798</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>two gentlemen conferring privately in a Virginia study, a manuscript between them, shutters half closed</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1798. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: two gentlemen conferring privately in a Virginia study, a manuscript between them, shutters half closed. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>kentucky_resolutions.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>xyz_affair</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>The XYZ Affair</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>1798</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>three masked men in fine clothes holding out their hands for a purse before an American envoy who refuses</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1798. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: three masked men in fine clothes holding out their hands for a purse before an American envoy who refuses. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>xyz_affair.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>marbury</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>1803</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>the Chief Justice in a black robe reading an opinion in a small candlelit courtroom</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1803. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: the Chief Justice in a black robe reading an opinion in a small candlelit courtroom. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>marbury.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>louisiana_purchase</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>The Louisiana Purchase</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>1803</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>a French flag lowered and an American flag raised over a square in New Orleans, ships on the river</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1803. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a French flag lowered and an American flag raised over a square in New Orleans, ships on the river. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>louisiana_purchase.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>burr_conspiracy</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>The Burr Conspiracy</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>1807</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>a gentleman in a long cloak standing trial in a crowded courtroom, guards at his side</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1807. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a gentleman in a long cloak standing trial in a crowded courtroom, guards at his side. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>burr_conspiracy.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>chesapeake_affair</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>The Chesapeake Affair</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>1807</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>a British warship firing a broadside into an American frigate at close range on a calm sea</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1807. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a British warship firing a broadside into an American frigate at close range on a calm sea. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>chesapeake_affair.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>embargo_act</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>The Embargo Act</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1807</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>idle merchant ships with furled sails at a quiet wharf, grass growing between the planks, sailors sitting idle</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1807. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: idle merchant ships with furled sails at a quiet wharf, grass growing between the planks, sailors sitting idle. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>embargo_act.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>niles_register</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Niles' Weekly Register</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Media event</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>1811</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>a reader in spectacles in an armchair surrounded by bound volumes of a weekly journal, prices and speeches pinned on the wall</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1811. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a reader in spectacles in an armchair surrounded by bound volumes of a weekly journal, prices and speeches pinned on the wall. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>niles_register.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>tippecanoe</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Tippecanoe</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>1811</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>a battle at dawn in a wooded river valley, militia firing from behind trees, a general on a white horse</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1811. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a battle at dawn in a wooded river valley, militia firing from behind trees, a general on a white horse. Depict every person with dignity and individual character, as a sympathetic period illustrator would; no caricature. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>tippecanoe.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>war_of_1812</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Mr. Madison's War</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>1812</v>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>an American frigate dueling a British frigate under full sail, cannon smoke billowing</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1812. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: an American frigate dueling a British frigate under full sail, cannon smoke billowing. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>war_of_1812.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>gerrymander</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>The Gerrymander</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>1812</v>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>a monstrous winged salamander-dragon made of the outline of a political district, with claws and teeth, drawn as a map</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1812. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a monstrous winged salamander-dragon made of the outline of a political district, with claws and teeth, drawn as a map. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>gerrymander.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>hartford_convention</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>The Hartford Convention</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>1814</v>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>grim gentlemen in black coats meeting behind closed shutters by lamplight in a New England hall</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1814. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: grim gentlemen in black coats meeting behind closed shutters by lamplight in a New England hall. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>hartford_convention.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>treaty_of_ghent</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>The Treaty of Ghent</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>1814</v>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>British and American diplomats shaking hands across a table in a Flemish chamber</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1814. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: British and American diplomats shaking hands across a table in a Flemish chamber. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>treaty_of_ghent.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>second_bank</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>The Second Bank of the United States</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>1816</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>a Greek-temple bank on a Philadelphia street with a crowd outside, banknotes fluttering</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1816. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a Greek-temple bank on a Philadelphia street with a crowd outside, banknotes fluttering. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>second_bank.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>tariff_of_1816</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>The Tariff of 1816</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>1816</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>a customs house on a busy wharf, crates of imported cloth stacked and weighed by officials</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1816. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a customs house on a busy wharf, crates of imported cloth stacked and weighed by officials. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>tariff_of_1816.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>cumberland_road</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>The Cumberland Road</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>1818</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Conestoga wagons and a stagecoach on a stone-paved road crossing a stone bridge in the mountains</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1818. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: Conestoga wagons and a stagecoach on a stone-paved road crossing a stone bridge in the mountains. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>cumberland_road.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>mcculloch</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>McCulloch v. Maryland</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>1819</v>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>the Supreme Court bench with robed justices, a lawyer arguing before them, a bank note on the table</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1819. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: the Supreme Court bench with robed justices, a lawyer arguing before them, a bank note on the table. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>mcculloch.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>adams_onis</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>The Adams-Onis Treaty</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>1819</v>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>a Spanish envoy and an American Secretary of State signing a treaty beside a large map with a line drawn to the Pacific</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1819. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a Spanish envoy and an American Secretary of State signing a treaty beside a large map with a line drawn to the Pacific. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>adams_onis.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>panic_of_1819</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>The Panic of 1819</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>1819</v>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>a crowd of anxious depositors at the shut doors of a bank, a sheriff posting a foreclosure notice</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1819. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a crowd of anxious depositors at the shut doors of a bank, a sheriff posting a foreclosure notice. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>panic_of_1819.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>missouri_compromise</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>The Missouri Compromise</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>a fire bell ringing in a dark tower at night over a sleeping town</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1820. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: a fire bell ringing in a dark tower at night over a sleeping town. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>missouri_compromise.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>denmark_vesey</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Denmark Vesey</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>1822</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>a dignified Black carpenter standing calm and upright in a Charleston courtroom before stern white judges</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1822. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: a dignified Black carpenter standing calm and upright in a Charleston courtroom before stern white judges. Depict every person with dignity and individual character, as a sympathetic period illustrator would; no caricature. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>denmark_vesey.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>crawford_radicals</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>The Crawford Radicals</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>1823</v>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>politicians in a smoky caucus room voting by candlelight, many chairs empty</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1823. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: politicians in a smoky caucus room voting by candlelight, many chairs empty. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>crawford_radicals.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>monroe_doctrine</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>The Monroe Doctrine</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>1823</v>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>an American eagle spreading its wings over a map of the western hemisphere as European warships turn away</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1823. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: an American eagle spreading its wings over a map of the western hemisphere as European warships turn away. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>monroe_doctrine.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>american_system</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>The American System</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>1824</v>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>a factory, a canal, a road and a bank arranged around a farmer's field, an allegory of national improvement</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1824. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: a factory, a canal, a road and a bank arranged around a farmer's field, an allegory of national improvement. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>american_system.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>erie_canal</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>The Erie Canal</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>1825</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>a canal boat pulled by mules along a towpath past locks, a canal town behind</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1825. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: a canal boat pulled by mules along a towpath past locks, a canal town behind. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>erie_canal.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>lowell_mills</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>The Lowell Mills</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>1826</v>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>young women mill workers walking in rows to a large brick textile mill beside a river at dawn</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1826. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: young women mill workers walking in rows to a large brick textile mill beside a river at dawn. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>lowell_mills.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>freedoms_journal</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Freedom's Journal</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>1827</v>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Black editors at work in a New York print office, one reading a proof sheet, a hand press in the background</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1827. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: Black editors at work in a New York print office, one reading a proof sheet, a hand press in the background. Depict every person with dignity and individual character, as a sympathetic period illustrator would; no caricature. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>freedoms_journal.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>anti_masonic_party</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>The Anti-Masonic Party</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>a crowd at a torchlit rally around a speaker holding up a Masonic apron and compass</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1828. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: a crowd at a torchlit rally around a speaker holding up a Masonic apron and compass. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>anti_masonic_party.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>cherokee_phoenix</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>The Cherokee Phoenix</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>a Cherokee printer at a hand press in a log print shop at New Echota, a newspaper page in the syllabary on the press</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1828. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: a Cherokee printer at a hand press in a log print shop at New Echota, a newspaper page in the syllabary on the press. Depict every person with dignity and individual character, as a sympathetic period illustrator would; no caricature. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>cherokee_phoenix.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>sc_exposition</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>The South Carolina Exposition</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>a gaunt statesman with a shock of hair writing at night by a single candle, a palmetto tree outside the window</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1828. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: a gaunt statesman with a shock of hair writing at night by a single candle, a palmetto tree outside the window. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>sc_exposition.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>tariff_abominations</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>The Tariff of Abominations</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>a monstrous many-headed creature made of crates and bales labelled with goods, menacing a cotton field</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1828. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: a monstrous many-headed creature made of crates and bales labelled with goods, menacing a cotton field. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>tariff_abominations.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>cotton_boom</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>The Cotton Boom</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>1830</v>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>cotton bales piled high on a river steamboat landing, ships waiting downstream</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1830. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: cotton bales piled high on a river steamboat landing, ships waiting downstream. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>cotton_boom.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>indian_removal</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>The Indian Removal Act</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>1830</v>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>a line of Cherokee families walking west through a winter forest with carts and blankets, soldiers riding alongside</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1830. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: a line of Cherokee families walking west through a winter forest with carts and blankets, soldiers riding alongside. Depict every person with dignity and individual character, as a sympathetic period illustrator would; no caricature. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>indian_removal.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>webster_hayne</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>The Webster-Hayne Debate</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>1830</v>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>a senator with a dark brow orating in the Senate chamber, hand raised, the galleries packed and silent</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1830. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: a senator with a dark brow orating in the Senate chamber, hand raised, the galleries packed and silent. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>webster_hayne.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>the_liberator</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>The Liberator</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>1831</v>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>a printer and editor in a cramped Boston garret printing a weekly paper by lamplight</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1831. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: a printer and editor in a cramped Boston garret printing a weekly paper by lamplight. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>the_liberator.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>bank_war</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>The Bank War</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>1832</v>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Jackson with a cane confronting a many-headed hydra emerging from a classical bank building</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1832. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: Andrew Jackson with a cane confronting a many-headed hydra emerging from a classical bank building. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>bank_war.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>force_bill</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>The Force Bill</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>1833</v>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>federal soldiers and a revenue cutter in Charleston harbor, cannon trained on a fort</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1833. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: federal soldiers and a revenue cutter in Charleston harbor, cannon trained on a fort. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>force_bill.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>penny_press</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>The Penny Press</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Media event</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>1833</v>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>newsboys shouting in a crowded New York street holding up papers, gas lamps and omnibuses behind</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1833. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: newsboys shouting in a crowded New York street holding up papers, gas lamps and omnibuses behind. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>penny_press.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>gag_rule</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>The Gag Rule</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>a congressman pushing a tall stack of petitions off the House clerk's desk while an old member rises to object</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1836, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a congressman pushing a tall stack of petitions off the House clerk's desk while an old member rises to object. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>gag_rule.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>specie_circular</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>The Specie Circular</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>a land-office counter where a settler empties a purse of gold and silver coins while paper notes are refused</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1836, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a land-office counter where a settler empties a purse of gold and silver coins while paper notes are refused. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>specie_circular.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>panic_of_1837</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>The Panic of 1837</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>1837</v>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>a bank run on a city street, crowds pressing on shut doors, a sign of suspended payment, a broken merchant on the curb</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1837, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a bank run on a city street, crowds pressing on shut doors, a sign of suspended payment, a broken merchant on the curb. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>panic_of_1837.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>amistad</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>The Amistad</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>1839</v>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>a schooner at anchor off Long Island with a group of African captives standing proud on its deck</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1839, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a schooner at anchor off Long Island with a group of African captives standing proud on its deck. Depict every person with dignity and individual character, as a sympathetic period illustrator would; no caricature. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>amistad.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>log_cabin_campaign</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Log Cabin and Hard Cider</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>1840</v>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>a log cabin with a barrel of hard cider by the door, a coonskin on the wall and a crowd of cheering Whigs with banners</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1840, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a log cabin with a barrel of hard cider by the door, a coonskin on the wall and a crowd of cheering Whigs with banners. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>log_cabin_campaign.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>tyler_vetoes</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>His Accidency's Vetoes</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>1841</v>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>a lone president at his desk signing a veto as cabinet members walk out of the room in a body</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1841, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a lone president at his desk signing a veto as cabinet members walk out of the room in a body. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>tyler_vetoes.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>dorr_rebellion</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>The Dorr Rebellion</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>1842</v>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>a ragtag militia with an old cannon outside the Providence arsenal at night in fog</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1842, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a ragtag militia with an old cannon outside the Providence arsenal at night in fog. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>dorr_rebellion.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>webster_ashburton</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>The Webster-Ashburton Treaty</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>1842</v>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>two diplomats shaking hands over a map of the Maine border, lumberjacks felling pines in the window behind</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1842, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: two diplomats shaking hands over a map of the Maine border, lumberjacks felling pines in the window behind. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>webster_ashburton.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>telegraph</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>The Magnetic Telegraph</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Media event</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>1844</v>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>a telegraph operator tapping a key at a desk, telegraph poles and wire running across the countryside through the window</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1844, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a telegraph operator tapping a key at a desk, telegraph poles and wire running across the countryside through the window. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>telegraph.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>texas_annexation</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>The Annexation of Texas</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>1845</v>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>a lone-star flag lowered and the American flag raised over the steps of a frontier capitol</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1845, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a lone-star flag lowered and the American flag raised over the steps of a frontier capitol. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>texas_annexation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>oregon_treaty</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Fifty-four Forty</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>1846</v>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>covered wagons crossing a vast western prairie toward snowy mountains</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1846, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: covered wagons crossing a vast western prairie toward snowy mountains. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>oregon_treaty.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>associated_press</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>The Associated Press</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Media event</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>1846</v>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>a steamship arriving at a New York wharf as reporters race in small boats to collect dispatches</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1846, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a steamship arriving at a New York wharf as reporters race in small boats to collect dispatches. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>associated_press.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>mexican_war</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>The Mexican War</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>1846</v>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>American troops storming a hilltop castle in a cloud of cannon smoke, the castle walls high above</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1846, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: American troops storming a hilltop castle in a cloud of cannon smoke, the castle walls high above. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>mexican_war.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>wilmot_proviso</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>The Wilmot Proviso</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>1846</v>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>a congressman standing in the crowded House chamber reading a short amendment, the members in uproar</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1846, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a congressman standing in the crowded House chamber reading a short amendment, the members in uproar. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>wilmot_proviso.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>rotary_press</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>The Rotary Press</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Media event</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>1847</v>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>a huge rotary printing press with great cylinders and pressmen feeding sheets, pulleys and belts overhead</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1847, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a huge rotary printing press with great cylinders and pressmen feeding sheets, pulleys and belts overhead. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>rotary_press.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>free_soil</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>The Free Soil Party</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>1848</v>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>a farmer with a plough on open western land under a rising sun, his family at the cabin door</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1848, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a farmer with a plough on open western land under a rising sun, his family at the cabin door. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>free_soil.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>gold_rush</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>The Gold Rush</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>1849</v>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>miners panning for gold in a mountain stream, tents and a sluice box, a clipper ship in a bay below</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1849, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: miners panning for gold in a mountain stream, tents and a sluice box, a clipper ship in a bay below. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>gold_rush.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>compromise_1850</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>The Compromise of 1850</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>1850</v>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>an aged senator addressing the Senate, gesturing to a scroll, senators leaning in</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1850, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: an aged senator addressing the Senate, gesturing to a scroll, senators leaning in. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>compromise_1850.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>fugitive_slave_act</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>The Fugitive Slave Act</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>1850</v>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>a crowd of Boston citizens confronting marshals leading a manacled Black man toward the harbor</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1850, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a crowd of Boston citizens confronting marshals leading a manacled Black man toward the harbor. Depict every person with dignity and individual character, as a sympathetic period illustrator would; no caricature. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>fugitive_slave_act.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>georgia_platform</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>The Georgia Platform</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>1850</v>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>a convention of Georgia delegates voting by raised hands in a state house hall</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1850, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a convention of Georgia delegates voting by raised hands in a state house hall. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>georgia_platform.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>nashville_convention</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>The Nashville Convention</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>1850</v>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>southern delegates meeting in a Nashville hall, a large map of the territories on the wall</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1850, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: southern delegates meeting in a Nashville hall, a large map of the territories on the wall. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>nashville_convention.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>cheap_postage</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>The Cheap Postage Act</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Media event</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>1851</v>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>a country post office with a postmaster sorting bundles of weekly newspapers into pigeonholes</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1851, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a country post office with a postmaster sorting bundles of weekly newspapers into pigeonholes. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>cheap_postage.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>uncle_toms_cabin</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Uncle Tom's Cabin</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>1852</v>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>a mother carrying her child across ice floes on a river at night, fleeing</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1852, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a mother carrying her child across ice floes on a river at night, fleeing. Depict every person with dignity and individual character, as a sympathetic period illustrator would; no caricature. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>uncle_toms_cabin.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>transcontinental_railroad</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>The Pacific Railroad Surveys</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>1853</v>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>surveyors with theodolites on a western plain, a steam locomotive drawn faintly in the distance</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1853, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: surveyors with theodolites on a western plain, a steam locomotive drawn faintly in the distance. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>transcontinental_railroad.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>gadsden_purchase</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>The Gadsden Purchase</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>1854</v>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>a desert landscape with saguaro cactus and a surveyor's flag, a railroad grade traced across it</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1854, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a desert landscape with saguaro cactus and a surveyor's flag, a railroad grade traced across it. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>gadsden_purchase.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>kansas_nebraska</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>The Kansas-Nebraska Act</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>1854</v>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>a prairie divided by a torn map line, settlers' cabins on both sides, a storm gathering</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1854, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a prairie divided by a torn map line, settlers' cabins on both sides, a storm gathering. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>kansas_nebraska.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>ostend_manifesto</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>The Ostend Manifesto</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>1854</v>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>three diplomats in a European parlor pointing at a map of Cuba, a fourth man peering through the door</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1854, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: three diplomats in a European parlor pointing at a map of Cuba, a fourth man peering through the door. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>ostend_manifesto.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>personal_liberty_laws</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>The Personal Liberty Laws</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>1855</v>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>a northern courthouse where townspeople block the doors against a federal marshal</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1855, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a northern courthouse where townspeople block the doors against a federal marshal. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>personal_liberty_laws.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>bleeding_kansas</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Bleeding Kansas</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>1856</v>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>a burning frontier town, men with rifles in the street and smoke over the prairie</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1856, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a burning frontier town, men with rifles in the street and smoke over the prairie. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>bleeding_kansas.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>sumner_caning</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>The Caning of Charles Sumner</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>1856</v>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>a congressman beating a seated senator with a cane on the Senate floor, the senator trapped under his desk</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1856, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a congressman beating a seated senator with a cane on the Senate floor, the senator trapped under his desk. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>sumner_caning.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>filibusters</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>The Filibusters</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>1856</v>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>a small band of armed adventurers wading ashore from a steamer onto a tropical beach under palm trees</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1856, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a small band of armed adventurers wading ashore from a steamer onto a tropical beach under palm trees. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>filibusters.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>dred_scott</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Dred Scott v. Sandford</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Economic story</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>1857</v>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>a dignified Black man and his wife standing together on the steps of a St. Louis courthouse</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1857, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a dignified Black man and his wife standing together on the steps of a St. Louis courthouse. Depict every person with dignity and individual character, as a sympathetic period illustrator would; no caricature. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>dred_scott.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>lecompton_constitution</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>The Lecompton Constitution</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>1857</v>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>a ballot box guarded by armed men in a frontier town, voters turned away</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1857, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a ballot box guarded by armed men in a frontier town, voters turned away. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>lecompton_constitution.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>freeport_doctrine</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>The Freeport Doctrine</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>1858</v>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>two politicians debating on a wooden platform in a small Illinois town square before a large crowd</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1858, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: two politicians debating on a wooden platform in a small Illinois town square before a large crowd. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>freeport_doctrine.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>lincoln_douglas</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>The Lincoln-Douglas Debates</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Political story</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>1858</v>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>a tall lanky man and a short stocky man debating on an outdoor platform before a huge crowd, reporters writing below</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1858, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a tall lanky man and a short stocky man debating on an outdoor platform before a huge crowd, reporters writing below. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>lincoln_douglas.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>ableman_v_booth</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Ableman v. Booth</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Social story</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>1859</v>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>an editor addressing a crowd outside a Milwaukee jail, the courthouse dome behind</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1859, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: an editor addressing a crowd outside a Milwaukee jail, the courthouse dome behind. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>ableman_v_booth.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>john_browns_raid</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>John Brown at Harpers Ferry</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Negative story</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>1859</v>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>a brick engine house under siege by marines at dawn, its doors being battered in</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1859, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: a brick engine house under siege by marines at dawn, its doors being battered in. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>john_browns_raid.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>1796-nation</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>The Federalist Administration (John Adams 1796)</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>1796</v>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>John Adams in a formal coat at a desk in Federal Hall, Washington's farewell address on the table before him</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1796. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: John Adams in a formal coat at a desk in Federal Hall, Washington's farewell address on the table before him. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>1796-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>1796-states</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>The Republican Societies (Thomas Jefferson 1796)</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>1796</v>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>a Democratic-Republican society meeting in a tavern, mechanics toasting liberty, Thomas Jefferson's portrait on the wall</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1796. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: a Democratic-Republican society meeting in a tavern, mechanics toasting liberty, Thomas Jefferson's portrait on the wall. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>1796-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>1800-nation</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>The Alien and Sedition Acts (John Adams 1800)</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>John Adams signing papers as a marshal leads a printer away through the window behind him</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1800. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: John Adams signing papers as a marshal leads a printer away through the window behind him. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>1800-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>1800-states</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>The Revolution of 1800 (Thomas Jefferson 1800)</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson walking alone to his inauguration through the unfinished capital, crowds cheering</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1800. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: Thomas Jefferson walking alone to his inauguration through the unfinished capital, crowds cheering. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>1800-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>1804-nation</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>The Louisiana Purchase (Thomas Jefferson 1804)</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>1804</v>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson studying a great map of the West, the Mississippi and New Orleans marked</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1804. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: Thomas Jefferson studying a great map of the West, the Mississippi and New Orleans marked. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>1804-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>1804-states</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>Federalist Commerce (Charles C. Pinckney 1804)</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>1804</v>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>Charles Cotesworth Pinckney on a busy Charleston wharf among merchant ships and cotton bales</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1804. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: Charles Cotesworth Pinckney on a busy Charleston wharf among merchant ships and cotton bales. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>1804-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>1808-nation</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>The Embargo (James Madison 1808)</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>1808</v>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>James Madison at a desk beneath a window showing empty ships idle in harbor</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1808. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: James Madison at a desk beneath a window showing empty ships idle in harbor. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>1808-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>1808-states</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>Free Trade and Sailors' Rights (Charles C. Pinckney 1808)</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>1808</v>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>Charles Cotesworth Pinckney beside a sailor with a banner, a merchant ship putting out to sea</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1808. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: Charles Cotesworth Pinckney beside a sailor with a banner, a merchant ship putting out to sea. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>1808-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>1812-nation</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>Mr. Madison's War (James Madison 1812)</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>1812</v>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>James Madison reviewing troops before a burning capital at night</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1812. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: James Madison reviewing troops before a burning capital at night. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>1812-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>1812-states</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>The Peace Ticket (DeWitt Clinton 1812)</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>1812</v>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>DeWitt Clinton on a New York dock as merchants cheer, ships ready to sail in peace</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1812. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: DeWitt Clinton on a New York dock as merchants cheer, ships ready to sail in peace. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>1812-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>1816-nation</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>The Era of Good Feelings (James Monroe 1816)</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>1816</v>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>James Monroe on horseback greeted by a cheering crowd on a goodwill tour of New England</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1816. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: James Monroe on horseback greeted by a cheering crowd on a goodwill tour of New England. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>1816-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>1816-states</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>The Last Federalist (Rufus King 1816)</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>1816</v>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>woodcut</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>Rufus King, an elderly Federalist statesman, standing alone in an empty party hall</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>Early American newspaper woodcut, c. 1816. A crude hand-cut woodblock print: bold solid black masses, white-line cutting, coarse parallel gouge marks for sky, water and ground, flat naive perspective, uneven ink and press grain, black ink on cream rag paper, a heavy double-rule border, like a cut from a colonial broadside or almanac. Subject: Rufus King, an elderly Federalist statesman, standing alone in an empty party hall. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>1816-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>1820-nation</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>An Antislavery Diary (John Quincy Adams 1820)</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>John Quincy Adams writing in his diary late at night by candlelight, a globe beside him</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1820. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: John Quincy Adams writing in his diary late at night by candlelight, a globe beside him. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>1820-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>1820-states</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>The Missouri Compromise (James Monroe 1820)</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>James Monroe signing a bill as congressmen draw a line across a map of the West</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1820. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: James Monroe signing a bill as congressmen draw a line across a map of the West. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>1820-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>1824-nation</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>The Corrupt Bargain (John Quincy Adams 1824)</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>1824</v>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>John Quincy Adams and Henry Clay shaking hands in a dim parlor, a third figure watching from the door</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1824. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: John Quincy Adams and Henry Clay shaking hands in a dim parlor, a third figure watching from the door. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>1824-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>1824-states</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>The People's Choice (Andrew Jackson 1824)</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>1824</v>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Jackson on horseback greeted by a vast cheering crowd of farmers and frontiersmen</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1824. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: Andrew Jackson on horseback greeted by a vast cheering crowd of farmers and frontiersmen. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>1824-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>1828-nation</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>The American System (John Quincy Adams 1828)</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>John Quincy Adams standing beside a canal lock and a new road, symbols of internal improvement</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1828. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: John Quincy Adams standing beside a canal lock and a new road, symbols of internal improvement. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>1828-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>1828-states</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>Jacksonian Democracy (Andrew Jackson 1828)</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>crowds of ordinary people pouring into the White House for Andrew Jackson's inauguration</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1828. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: crowds of ordinary people pouring into the White House for Andrew Jackson's inauguration. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>1828-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>1832-nation</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>The Bank Recharter (Henry Clay 1832)</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>1832</v>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>Henry Clay addressing the Senate, a classical bank building drawn behind him</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1832. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: Henry Clay addressing the Senate, a classical bank building drawn behind him. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>1832-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>1832-states</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>The Bank War (Andrew Jackson 1832)</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>1832</v>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>wood engraving</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>Andrew Jackson brandishing a veto before a toppling marble bank building</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>American wood engraving, c. 1832. A fine end-grain wood engraving as in a penny magazine or almanac of the 1820s and 1830s: crisp parallel lines and crosshatching for tone, careful detail, small figures, a thin rule border, black ink on off-white newsprint. Subject: Andrew Jackson brandishing a veto before a toppling marble bank building. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>1832-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>1836-nation</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>The Whig Coalition (William Henry Harrison 1836)</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>William Henry Harrison in a frontier coat at the head of a regional Whig rally</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1836, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: William Henry Harrison in a frontier coat at the head of a regional Whig rally. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>1836-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>1836-states</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>The Specie Circular (Martin Van Buren 1836)</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>1836</v>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>Martin Van Buren in a fine coat counting gold coins at a treasury counter</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1836, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: Martin Van Buren in a fine coat counting gold coins at a treasury counter. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>1836-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>1840-nation</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>Log Cabin and Hard Cider (William Henry Harrison 1840)</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>1840</v>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>William Henry Harrison at the door of a log cabin with a cider barrel, a parade with banners passing</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1840, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: William Henry Harrison at the door of a log cabin with a cider barrel, a parade with banners passing. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>1840-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>1840-states</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>The Independent Treasury (Martin Van Buren 1840)</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>1840</v>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>Martin Van Buren beside a strongbox in a vault, an independent treasury, guards at the door</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1840, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: Martin Van Buren beside a strongbox in a vault, an independent treasury, guards at the door. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>1840-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>1844-nation</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>The Raleigh Letter (Henry Clay 1844)</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>1844</v>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>Henry Clay at a writing desk drafting a letter, a map of Texas on the wall behind him</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1844, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: Henry Clay at a writing desk drafting a letter, a map of Texas on the wall behind him. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>1844-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>1844-states</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>Manifest Destiny (James K. Polk 1844)</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>1844</v>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>James K. Polk pointing west across a map of the continent to the Pacific</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1844, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: James K. Polk pointing west across a map of the continent to the Pacific. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>1844-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>1848-nation</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>Old Rough and Ready (Zachary Taylor 1848)</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>1848</v>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>Zachary Taylor in a plain coat and straw hat on his old warhorse, a military camp behind</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1848, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: Zachary Taylor in a plain coat and straw hat on his old warhorse, a military camp behind. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>1848-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>1848-states</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>Popular Sovereignty (Lewis Cass 1848)</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>1848</v>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>Lewis Cass addressing settlers on a western prairie, each family at its own ballot box</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1848, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: Lewis Cass addressing settlers on a western prairie, each family at its own ballot box. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>1848-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>1852-nation</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Old Fuss and Feathers (Winfield Scott 1852)</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>1852</v>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>Winfield Scott in full dress uniform with plumed hat, reviewing troops</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1852, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: Winfield Scott in full dress uniform with plumed hat, reviewing troops. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>1852-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>1852-states</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>The Compromise of 1850 (Franklin Pierce 1852)</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>1852</v>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>Franklin Pierce taking the oath of office in falling snow before the Capitol</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1852, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: Franklin Pierce taking the oath of office in falling snow before the Capitol. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>1852-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>1856-nation</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>Free Soil, Free Men, Fremont (John C. Fremont 1856)</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="n">
+        <v>1856</v>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>John C. Fremont on a mountain peak in the Rockies raising a flag, his expedition below</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1856, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: John C. Fremont on a mountain peak in the Rockies raising a flag, his expedition below. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>1856-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>1856-states</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>Bleeding Kansas (James Buchanan 1856)</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>1856</v>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>James Buchanan at a desk as the Kansas prairie burns in the window behind him</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1856, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: James Buchanan at a desk as the Kansas prairie burns in the window behind him. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>1856-states.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>1860-nation</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>A House Divided (Abraham Lincoln 1860)</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="n">
+        <v>1860</v>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>Abraham Lincoln standing tall in a dark coat, a rail fence and the unfinished Capitol dome behind him</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1860, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: Abraham Lincoln standing tall in a dark coat, a rail fence and the unfinished Capitol dome behind him. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>1860-nation.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>1860-states</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>The Little Giant (Stephen A. Douglas 1860)</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>Election</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>1860</v>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>lithograph</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>Stephen A. Douglas, short and stocky, speaking from a railway car platform to a crowd</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>American lithograph, c. 1860, in the manner of a Currier or Sarony print: soft crayon-on-stone tone, smooth gradations from deep black to paper white, stippled grain, highlights scraped out of the stone, naturalistic drawing, the scene fading in a soft oval vignette into cream paper. Subject: Stephen A. Douglas, short and stocky, speaking from a railway car platform to a crowd. Monochrome black ink on cream paper, no color, no hand-coloring. No lettering, captions, signatures or watermarks. Landscape 4:3 composition with the subject centered and readable at small size.</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>1860-states.png</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H145"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
